--- a/word-monitor-sitemap/report/latest.xlsx
+++ b/word-monitor-sitemap/report/latest.xlsx
@@ -54,12 +54,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,7 +451,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-07-10T15:31:14</t>
+          <t>2026-07-10T17:29:03</t>
         </is>
       </c>
     </row>
@@ -503,8 +514,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="31" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -579,158 +590,209 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>block sort jigsaw puzzle journey</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>https://www.crazygames.com/ar/game/block-sort---jigsaw-puzzle-journey | https://www.crazygames.com/cz/game/block-sort---jigsaw-puzzle-journey | https://www.crazygames.com/de/game/block-sort---jigsaw-puzzle-journey | https://www.crazygames.com/es/game/block-sort---jigsaw-puzzle-journey | https://www.crazygames.com/fi/game/block-sort---jigsaw-puzzle-journey | https://www.crazygames.com/gr/game/block-sort---jigsaw-puzzle-journey | https://www.crazygames.com/kr/game/block-sort---jigsaw-puzzle-journey | https://www.crazygames.com/pl/game/block-sort---jigsaw-puzzle-journey | https://www.crazygames.com/ru/game/block-sort---jigsaw-puzzle-journey | https://www.crazygames.com/se/game/block-sort---jigsaw-puzzle-journey</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="4" t="n"/>
-      <c r="K2" s="4" t="n"/>
-      <c r="L2" s="4" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/ar/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/cz/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/de/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/es/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/fi/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/gr/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/kr/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/pl/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/ru/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/se/game/block-sort---jigsaw-puzzle-journey</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="5" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>downhill racer bvk</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://www.crazygames.com/ar/game/downhill-racer-bvk | https://www.crazygames.com/es/game/downhill-racer-bvk | https://www.crazygames.com/fi/game/downhill-racer-bvk | https://www.crazygames.com/gr/game/downhill-racer-bvk | https://www.crazygames.com/kr/game/downhill-racer-bvk | https://www.crazygames.com/pl/game/downhill-racer-bvk | https://www.crazygames.com/se/game/downhill-racer-bvk</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="4" t="n"/>
-      <c r="K3" s="4" t="n"/>
-      <c r="L3" s="4" t="n"/>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/ar/game/downhill-racer-bvk
+https://www.crazygames.com/es/game/downhill-racer-bvk
+https://www.crazygames.com/fi/game/downhill-racer-bvk
+https://www.crazygames.com/gr/game/downhill-racer-bvk
+https://www.crazygames.com/kr/game/downhill-racer-bvk
+https://www.crazygames.com/pl/game/downhill-racer-bvk
+https://www.crazygames.com/se/game/downhill-racer-bvk</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>nightfall survivors imo</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://www.crazygames.com/ar/game/nightfall-survivors-imo | https://www.crazygames.com/br/game/nightfall-survivors-imo | https://www.crazygames.com/cz/game/nightfall-survivors-imo | https://www.crazygames.com/de/game/nightfall-survivors-imo | https://www.crazygames.com/es/game/nightfall-survivors-imo | https://www.crazygames.com/fi/game/nightfall-survivors-imo | https://www.crazygames.com/gr/game/nightfall-survivors-imo | https://www.crazygames.com/hu/game/nightfall-survivors-imo | https://www.crazygames.com/kr/game/nightfall-survivors-imo | https://www.crazygames.com/pl/game/nightfall-survivors-imo | https://www.crazygames.com/ro/game/nightfall-survivors-imo | https://www.crazygames.com/ru/game/nightfall-survivors-imo | https://www.crazygames.com/se/game/nightfall-survivors-imo</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="4" t="n"/>
-      <c r="K4" s="4" t="n"/>
-      <c r="L4" s="4" t="n"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/ar/game/nightfall-survivors-imo
+https://www.crazygames.com/br/game/nightfall-survivors-imo
+https://www.crazygames.com/cz/game/nightfall-survivors-imo
+https://www.crazygames.com/de/game/nightfall-survivors-imo
+https://www.crazygames.com/es/game/nightfall-survivors-imo
+https://www.crazygames.com/fi/game/nightfall-survivors-imo
+https://www.crazygames.com/gr/game/nightfall-survivors-imo
+https://www.crazygames.com/hu/game/nightfall-survivors-imo
+https://www.crazygames.com/kr/game/nightfall-survivors-imo
+https://www.crazygames.com/pl/game/nightfall-survivors-imo
+https://www.crazygames.com/ro/game/nightfall-survivors-imo
+https://www.crazygames.com/ru/game/nightfall-survivors-imo
+https://www.crazygames.com/se/game/nightfall-survivors-imo</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>pixel world uyv</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://www.crazygames.com/ar/game/pixel-world-uyv | https://www.crazygames.com/es/game/pixel-world-uyv | https://www.crazygames.com/fi/game/pixel-world-uyv | https://www.crazygames.com/gr/game/pixel-world-uyv | https://www.crazygames.com/kr/game/pixel-world-uyv | https://www.crazygames.com/pl/game/pixel-world-uyv | https://www.crazygames.com/se/game/pixel-world-uyv</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="n"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/ar/game/pixel-world-uyv
+https://www.crazygames.com/es/game/pixel-world-uyv
+https://www.crazygames.com/fi/game/pixel-world-uyv
+https://www.crazygames.com/gr/game/pixel-world-uyv
+https://www.crazygames.com/kr/game/pixel-world-uyv
+https://www.crazygames.com/pl/game/pixel-world-uyv
+https://www.crazygames.com/se/game/pixel-world-uyv</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>the flowers merge and sell bouquets</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://www.crazygames.com/ar/game/the-flowers-merge-and-sell-bouquets | https://www.crazygames.com/cz/game/the-flowers-merge-and-sell-bouquets | https://www.crazygames.com/de/game/the-flowers-merge-and-sell-bouquets | https://www.crazygames.com/es/game/the-flowers-merge-and-sell-bouquets | https://www.crazygames.com/fi/game/the-flowers-merge-and-sell-bouquets | https://www.crazygames.com/gr/game/the-flowers-merge-and-sell-bouquets | https://www.crazygames.com/kr/game/the-flowers-merge-and-sell-bouquets | https://www.crazygames.com/pl/game/the-flowers-merge-and-sell-bouquets | https://www.crazygames.com/ru/game/the-flowers-merge-and-sell-bouquets | https://www.crazygames.com/se/game/the-flowers-merge-and-sell-bouquets</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="n"/>
-      <c r="L6" s="4" t="n"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/ar/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/cz/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/de/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/es/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/fi/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/gr/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/kr/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/pl/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/ru/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/se/game/the-flowers-merge-and-sell-bouquets</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>travel merge</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>https://poki.com/en/g/travel-merge</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="n"/>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>unscrambled</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>https://www.crazygames.com/ar/game/unscrambled | https://www.crazygames.com/cz/game/unscrambled | https://www.crazygames.com/de/game/unscrambled | https://www.crazygames.com/es/game/unscrambled | https://www.crazygames.com/fi/game/unscrambled | https://www.crazygames.com/gr/game/unscrambled | https://www.crazygames.com/kr/game/unscrambled | https://www.crazygames.com/pl/game/unscrambled | https://www.crazygames.com/ru/game/unscrambled | https://www.crazygames.com/se/game/unscrambled</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="n"/>
-      <c r="L8" s="4" t="n"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/ar/game/unscrambled
+https://www.crazygames.com/cz/game/unscrambled
+https://www.crazygames.com/de/game/unscrambled
+https://www.crazygames.com/es/game/unscrambled
+https://www.crazygames.com/fi/game/unscrambled
+https://www.crazygames.com/gr/game/unscrambled
+https://www.crazygames.com/kr/game/unscrambled
+https://www.crazygames.com/pl/game/unscrambled
+https://www.crazygames.com/ru/game/unscrambled
+https://www.crazygames.com/se/game/unscrambled</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L8"/>

--- a/word-monitor-sitemap/report/latest.xlsx
+++ b/word-monitor-sitemap/report/latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="keywords" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,11 +436,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -451,51 +451,77 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-07-10T17:29:03</t>
+          <t>2026-07-11T16:04:37</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>stamp</t>
+          <t>standardWordTableVersion</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260710-133103</t>
+          <t>v1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>siteCount</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>7</v>
+          <t>scoreFormula</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>simWindowVolume * simCpc / simKd</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>standardWordRows</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>7</v>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>check-gefei-kd</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>standardWordTableVersion</t>
+          <t>inputMode</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>standard_word_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>rowCount</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>gefeiKdSummary</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>{"inputCount": 9, "requestCount": 9, "successCount": 9, "successWithScoreCount": 9, "missingScoreCount": 0, "failedCount": 0}</t>
         </is>
       </c>
     </row>
@@ -510,12 +536,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
     <col width="64" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="31" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -592,210 +618,522 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>block sort jigsaw puzzle journey</t>
+          <t>green</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/ar/game/block-sort---jigsaw-puzzle-journey
-https://www.crazygames.com/cz/game/block-sort---jigsaw-puzzle-journey
-https://www.crazygames.com/de/game/block-sort---jigsaw-puzzle-journey
-https://www.crazygames.com/es/game/block-sort---jigsaw-puzzle-journey
-https://www.crazygames.com/fi/game/block-sort---jigsaw-puzzle-journey
-https://www.crazygames.com/gr/game/block-sort---jigsaw-puzzle-journey
-https://www.crazygames.com/kr/game/block-sort---jigsaw-puzzle-journey
-https://www.crazygames.com/pl/game/block-sort---jigsaw-puzzle-journey
-https://www.crazygames.com/ru/game/block-sort---jigsaw-puzzle-journey
-https://www.crazygames.com/se/game/block-sort---jigsaw-puzzle-journey</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="4" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
-      <c r="L2" s="5" t="n"/>
+          <t>https://www.crazygames.com/ar/game/green
+https://www.crazygames.com/br/game/green
+https://www.crazygames.com/cz/game/green
+https://www.crazygames.com/de/game/green
+https://www.crazygames.com/dk/game/green
+https://www.crazygames.com/es/game/green
+https://www.crazygames.com/fi/game/green
+https://www.crazygames.com/fr/game/green
+https://www.crazygames.com/game/green
+https://www.crazygames.com/gr/game/green
+https://www.crazygames.com/hu/game/green
+https://www.crazygames.com/id/game/green
+https://www.crazygames.com/it/game/green
+https://www.crazygames.com/jp/game/green
+https://www.crazygames.com/kr/game/green
+https://www.crazygames.com/nl/game/green
+https://www.crazygames.com/no/game/green
+https://www.crazygames.com/pl/game/green
+https://www.crazygames.com/ro/game/green
+https://www.crazygames.com/ru/game/green
+https://www.crazygames.com/se/game/green
+https://www.crazygames.com/th/game/green
+https://www.crazygames.com/tr/game/green
+https://www.crazygames.com/ua/game/green
+https://www.crazygames.com/vn/game/green</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>54518.094</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>833610.0</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>1257960.0</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>47.0</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>4.74</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>66.3</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>downhill racer bvk</t>
+          <t>unscrambled</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/ar/game/downhill-racer-bvk
-https://www.crazygames.com/es/game/downhill-racer-bvk
-https://www.crazygames.com/fi/game/downhill-racer-bvk
-https://www.crazygames.com/gr/game/downhill-racer-bvk
-https://www.crazygames.com/kr/game/downhill-racer-bvk
-https://www.crazygames.com/pl/game/downhill-racer-bvk
-https://www.crazygames.com/se/game/downhill-racer-bvk</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="4" t="n"/>
-      <c r="J3" s="5" t="n"/>
-      <c r="K3" s="5" t="n"/>
-      <c r="L3" s="5" t="n"/>
+          <t>https://www.crazygames.com/br/game/unscrambled
+https://www.crazygames.com/dk/game/unscrambled
+https://www.crazygames.com/fr/game/unscrambled
+https://www.crazygames.com/game/unscrambled
+https://www.crazygames.com/hu/game/unscrambled
+https://www.crazygames.com/id/game/unscrambled
+https://www.crazygames.com/it/game/unscrambled
+https://www.crazygames.com/jp/game/unscrambled
+https://www.crazygames.com/nl/game/unscrambled
+https://www.crazygames.com/no/game/unscrambled
+https://www.crazygames.com/ro/game/unscrambled
+https://www.crazygames.com/th/game/unscrambled
+https://www.crazygames.com/tr/game/unscrambled
+https://www.crazygames.com/ua/game/unscrambled
+https://www.crazygames.com/vn/game/unscrambled</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>unscrambled</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>36.685106</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>4660.0</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>47.0</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>183690.0</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>70.5</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>nightfall survivors imo</t>
+          <t>dd 2k shoot</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/ar/game/nightfall-survivors-imo
-https://www.crazygames.com/br/game/nightfall-survivors-imo
-https://www.crazygames.com/cz/game/nightfall-survivors-imo
-https://www.crazygames.com/de/game/nightfall-survivors-imo
-https://www.crazygames.com/es/game/nightfall-survivors-imo
-https://www.crazygames.com/fi/game/nightfall-survivors-imo
-https://www.crazygames.com/gr/game/nightfall-survivors-imo
-https://www.crazygames.com/hu/game/nightfall-survivors-imo
-https://www.crazygames.com/kr/game/nightfall-survivors-imo
-https://www.crazygames.com/pl/game/nightfall-survivors-imo
-https://www.crazygames.com/ro/game/nightfall-survivors-imo
-https://www.crazygames.com/ru/game/nightfall-survivors-imo
-https://www.crazygames.com/se/game/nightfall-survivors-imo</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
+          <t>https://www.coolmathgames.com/0-dd-2k-shoot</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>dd 2k shoot</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="4" t="n"/>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
-      <c r="I4" s="4" t="n"/>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
       <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
-      <c r="L4" s="5" t="n"/>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>pixel world uyv</t>
+          <t>backrooms recovery</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/ar/game/pixel-world-uyv
-https://www.crazygames.com/es/game/pixel-world-uyv
-https://www.crazygames.com/fi/game/pixel-world-uyv
-https://www.crazygames.com/gr/game/pixel-world-uyv
-https://www.crazygames.com/kr/game/pixel-world-uyv
-https://www.crazygames.com/pl/game/pixel-world-uyv
-https://www.crazygames.com/se/game/pixel-world-uyv</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
+          <t>https://poki.com/en/g/backrooms-recovery</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>backrooms recovery</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
       <c r="E5" s="3" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="4" t="n"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1260.0</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J5" s="5" t="n"/>
       <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>47.3</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>the flowers merge and sell bouquets</t>
+          <t>block sort jigsaw puzzle journey</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/ar/game/the-flowers-merge-and-sell-bouquets
-https://www.crazygames.com/cz/game/the-flowers-merge-and-sell-bouquets
-https://www.crazygames.com/de/game/the-flowers-merge-and-sell-bouquets
-https://www.crazygames.com/es/game/the-flowers-merge-and-sell-bouquets
-https://www.crazygames.com/fi/game/the-flowers-merge-and-sell-bouquets
-https://www.crazygames.com/gr/game/the-flowers-merge-and-sell-bouquets
-https://www.crazygames.com/kr/game/the-flowers-merge-and-sell-bouquets
-https://www.crazygames.com/pl/game/the-flowers-merge-and-sell-bouquets
-https://www.crazygames.com/ru/game/the-flowers-merge-and-sell-bouquets
-https://www.crazygames.com/se/game/the-flowers-merge-and-sell-bouquets</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
+          <t>https://www.crazygames.com/br/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/dk/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/fr/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/hu/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/id/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/it/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/jp/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/nl/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/no/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/ro/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/th/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/tr/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/ua/game/block-sort---jigsaw-puzzle-journey
+https://www.crazygames.com/vn/game/block-sort---jigsaw-puzzle-journey</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>block sort jigsaw puzzle journey</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="5" t="n"/>
-      <c r="I6" s="4" t="n"/>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J6" s="5" t="n"/>
       <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>63.6</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>travel merge</t>
+          <t>downhill racer bvk</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://poki.com/en/g/travel-merge</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr"/>
+          <t>https://www.crazygames.com/br/game/downhill-racer-bvk
+https://www.crazygames.com/cz/game/downhill-racer-bvk
+https://www.crazygames.com/de/game/downhill-racer-bvk
+https://www.crazygames.com/dk/game/downhill-racer-bvk
+https://www.crazygames.com/fr/game/downhill-racer-bvk
+https://www.crazygames.com/game/downhill-racer-bvk
+https://www.crazygames.com/hu/game/downhill-racer-bvk
+https://www.crazygames.com/id/game/downhill-racer-bvk
+https://www.crazygames.com/it/game/downhill-racer-bvk
+https://www.crazygames.com/jp/game/downhill-racer-bvk
+https://www.crazygames.com/nl/game/downhill-racer-bvk
+https://www.crazygames.com/no/game/downhill-racer-bvk
+https://www.crazygames.com/ro/game/downhill-racer-bvk
+https://www.crazygames.com/ru/game/downhill-racer-bvk
+https://www.crazygames.com/th/game/downhill-racer-bvk
+https://www.crazygames.com/tr/game/downhill-racer-bvk
+https://www.crazygames.com/ua/game/downhill-racer-bvk
+https://www.crazygames.com/vn/game/downhill-racer-bvk</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>downhill racer bvk</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="4" t="n"/>
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
-      <c r="I7" s="4" t="n"/>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J7" s="5" t="n"/>
       <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>33.8</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>unscrambled</t>
+          <t>nightfall survivors imo</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/ar/game/unscrambled
-https://www.crazygames.com/cz/game/unscrambled
-https://www.crazygames.com/de/game/unscrambled
-https://www.crazygames.com/es/game/unscrambled
-https://www.crazygames.com/fi/game/unscrambled
-https://www.crazygames.com/gr/game/unscrambled
-https://www.crazygames.com/kr/game/unscrambled
-https://www.crazygames.com/pl/game/unscrambled
-https://www.crazygames.com/ru/game/unscrambled
-https://www.crazygames.com/se/game/unscrambled</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
+          <t>https://www.crazygames.com/dk/game/nightfall-survivors-imo
+https://www.crazygames.com/fr/game/nightfall-survivors-imo
+https://www.crazygames.com/game/nightfall-survivors-imo
+https://www.crazygames.com/id/game/nightfall-survivors-imo
+https://www.crazygames.com/it/game/nightfall-survivors-imo
+https://www.crazygames.com/jp/game/nightfall-survivors-imo
+https://www.crazygames.com/nl/game/nightfall-survivors-imo
+https://www.crazygames.com/no/game/nightfall-survivors-imo
+https://www.crazygames.com/th/game/nightfall-survivors-imo
+https://www.crazygames.com/tr/game/nightfall-survivors-imo
+https://www.crazygames.com/ua/game/nightfall-survivors-imo
+https://www.crazygames.com/vn/game/nightfall-survivors-imo</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>nightfall survivors imo</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="4" t="n"/>
       <c r="G8" s="5" t="n"/>
       <c r="H8" s="5" t="n"/>
-      <c r="I8" s="4" t="n"/>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="J8" s="5" t="n"/>
       <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>32.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>pixel world uyv</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/br/game/pixel-world-uyv
+https://www.crazygames.com/cz/game/pixel-world-uyv
+https://www.crazygames.com/de/game/pixel-world-uyv
+https://www.crazygames.com/dk/game/pixel-world-uyv
+https://www.crazygames.com/fr/game/pixel-world-uyv
+https://www.crazygames.com/game/pixel-world-uyv
+https://www.crazygames.com/hu/game/pixel-world-uyv
+https://www.crazygames.com/id/game/pixel-world-uyv
+https://www.crazygames.com/it/game/pixel-world-uyv
+https://www.crazygames.com/jp/game/pixel-world-uyv
+https://www.crazygames.com/nl/game/pixel-world-uyv
+https://www.crazygames.com/no/game/pixel-world-uyv
+https://www.crazygames.com/ro/game/pixel-world-uyv
+https://www.crazygames.com/ru/game/pixel-world-uyv
+https://www.crazygames.com/th/game/pixel-world-uyv
+https://www.crazygames.com/tr/game/pixel-world-uyv
+https://www.crazygames.com/ua/game/pixel-world-uyv
+https://www.crazygames.com/vn/game/pixel-world-uyv</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>pixel world uyv</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>33.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>the flowers merge and sell bouquets</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/br/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/dk/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/fr/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/hu/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/id/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/it/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/jp/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/nl/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/no/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/ro/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/th/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/tr/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/ua/game/the-flowers-merge-and-sell-bouquets
+https://www.crazygames.com/vn/game/the-flowers-merge-and-sell-bouquets</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>the flowers merge and sell bouquets</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>47.3</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L8"/>
+  <autoFilter ref="A1:L10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/word-monitor-sitemap/report/latest.xlsx
+++ b/word-monitor-sitemap/report/latest.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="keywords" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -32,12 +34,22 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF4FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4EAFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,9 +64,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -422,11 +455,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -437,51 +470,77 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-07-12T13:15:59</t>
+          <t>2026-07-13T21:37:37</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>stamp</t>
+          <t>standardWordTableVersion</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260712-131358</t>
+          <t>v1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>siteCount</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>6</v>
+          <t>scoreFormula</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>simWindowVolume * simCpc / simKd</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>standardWordRows</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>check-gefei-kd</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>standardWordTableVersion</t>
+          <t>inputMode</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>standard_word_table</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>rowCount</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>gefeiKdSummary</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>{"inputCount": 9, "requestCount": 9, "successCount": 8, "successWithScoreCount": 8, "missingScoreCount": 0, "failedCount": 1}</t>
         </is>
       </c>
     </row>
@@ -496,11 +555,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -575,8 +634,488 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>om nom run</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.onlinegames.io/om-nom-run</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>13570</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>12830</v>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="I2" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J2" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>om nom run</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>jelly run</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.onlinegames.io/jelly-run-2048</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>36.625926</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>6380</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>7300</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="I3" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>jelly run</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>divine clash</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/ar/game/divine-clash
+https://www.crazygames.com/br/game/divine-clash
+https://www.crazygames.com/cz/game/divine-clash
+https://www.crazygames.com/de/game/divine-clash
+https://www.crazygames.com/dk/game/divine-clash
+https://www.crazygames.com/es/game/divine-clash
+https://www.crazygames.com/fi/game/divine-clash
+https://www.crazygames.com/fr/game/divine-clash
+https://www.crazygames.com/game/divine-clash
+https://www.crazygames.com/gr/game/divine-clash
+https://www.crazygames.com/hu/game/divine-clash
+https://www.crazygames.com/id/game/divine-clash
+https://www.crazygames.com/it/game/divine-clash
+https://www.crazygames.com/jp/game/divine-clash
+https://www.crazygames.com/kr/game/divine-clash
+https://www.crazygames.com/nl/game/divine-clash
+https://www.crazygames.com/no/game/divine-clash
+https://www.crazygames.com/pl/game/divine-clash
+https://www.crazygames.com/ro/game/divine-clash
+https://www.crazygames.com/ru/game/divine-clash
+https://www.crazygames.com/se/game/divine-clash
+https://www.crazygames.com/th/game/divine-clash
+https://www.crazygames.com/tr/game/divine-clash
+https://www.crazygames.com/ua/game/divine-clash
+https://www.crazygames.com/vn/game/divine-clash</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="4" t="n">
+        <v>1330</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
+      <c r="J4" s="8" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>divine clash</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>alphablitz wty</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/ar/game/alphablitz-wty
+https://www.crazygames.com/br/game/alphablitz-wty
+https://www.crazygames.com/cz/game/alphablitz-wty
+https://www.crazygames.com/de/game/alphablitz-wty
+https://www.crazygames.com/dk/game/alphablitz-wty
+https://www.crazygames.com/es/game/alphablitz-wty
+https://www.crazygames.com/fi/game/alphablitz-wty
+https://www.crazygames.com/fr/game/alphablitz-wty
+https://www.crazygames.com/game/alphablitz-wty
+https://www.crazygames.com/gr/game/alphablitz-wty
+https://www.crazygames.com/hu/game/alphablitz-wty
+https://www.crazygames.com/id/game/alphablitz-wty
+https://www.crazygames.com/it/game/alphablitz-wty
+https://www.crazygames.com/jp/game/alphablitz-wty
+https://www.crazygames.com/kr/game/alphablitz-wty
+https://www.crazygames.com/nl/game/alphablitz-wty
+https://www.crazygames.com/no/game/alphablitz-wty
+https://www.crazygames.com/pl/game/alphablitz-wty
+https://www.crazygames.com/ro/game/alphablitz-wty
+https://www.crazygames.com/ru/game/alphablitz-wty
+https://www.crazygames.com/se/game/alphablitz-wty
+https://www.crazygames.com/th/game/alphablitz-wty
+https://www.crazygames.com/tr/game/alphablitz-wty
+https://www.crazygames.com/ua/game/alphablitz-wty
+https://www.crazygames.com/vn/game/alphablitz-wty</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
+      <c r="J5" s="8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>alphablitz wty</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>farm mayhem merge</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/ar/game/farm-mayhem-merge
+https://www.crazygames.com/br/game/farm-mayhem-merge
+https://www.crazygames.com/cz/game/farm-mayhem-merge
+https://www.crazygames.com/de/game/farm-mayhem-merge
+https://www.crazygames.com/dk/game/farm-mayhem-merge
+https://www.crazygames.com/es/game/farm-mayhem-merge
+https://www.crazygames.com/fi/game/farm-mayhem-merge
+https://www.crazygames.com/fr/game/farm-mayhem-merge
+https://www.crazygames.com/game/farm-mayhem-merge
+https://www.crazygames.com/gr/game/farm-mayhem-merge
+https://www.crazygames.com/hu/game/farm-mayhem-merge
+https://www.crazygames.com/id/game/farm-mayhem-merge
+https://www.crazygames.com/it/game/farm-mayhem-merge
+https://www.crazygames.com/jp/game/farm-mayhem-merge
+https://www.crazygames.com/kr/game/farm-mayhem-merge
+https://www.crazygames.com/nl/game/farm-mayhem-merge
+https://www.crazygames.com/no/game/farm-mayhem-merge
+https://www.crazygames.com/pl/game/farm-mayhem-merge
+https://www.crazygames.com/ro/game/farm-mayhem-merge
+https://www.crazygames.com/ru/game/farm-mayhem-merge
+https://www.crazygames.com/se/game/farm-mayhem-merge
+https://www.crazygames.com/th/game/farm-mayhem-merge
+https://www.crazygames.com/tr/game/farm-mayhem-merge
+https://www.crazygames.com/ua/game/farm-mayhem-merge
+https://www.crazygames.com/vn/game/farm-mayhem-merge</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="8" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>farm mayhem merge</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>lafufu blind box dress up</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>https://poki.com/en/g/lafufu-blind-box-dress-up</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>lafufu blind box dress up</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>orecrusher</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/ar/game/orecrusher-2
+https://www.crazygames.com/br/game/orecrusher-2
+https://www.crazygames.com/cz/game/orecrusher-2
+https://www.crazygames.com/de/game/orecrusher-2
+https://www.crazygames.com/dk/game/orecrusher-2
+https://www.crazygames.com/es/game/orecrusher-2
+https://www.crazygames.com/fi/game/orecrusher-2
+https://www.crazygames.com/fr/game/orecrusher-2
+https://www.crazygames.com/game/orecrusher-2
+https://www.crazygames.com/gr/game/orecrusher-2
+https://www.crazygames.com/hu/game/orecrusher-2
+https://www.crazygames.com/id/game/orecrusher-2
+https://www.crazygames.com/it/game/orecrusher-2
+https://www.crazygames.com/jp/game/orecrusher-2
+https://www.crazygames.com/kr/game/orecrusher-2
+https://www.crazygames.com/nl/game/orecrusher-2
+https://www.crazygames.com/no/game/orecrusher-2
+https://www.crazygames.com/pl/game/orecrusher-2
+https://www.crazygames.com/ro/game/orecrusher-2
+https://www.crazygames.com/ru/game/orecrusher-2
+https://www.crazygames.com/se/game/orecrusher-2
+https://www.crazygames.com/th/game/orecrusher-2
+https://www.crazygames.com/tr/game/orecrusher-2
+https://www.crazygames.com/ua/game/orecrusher-2
+https://www.crazygames.com/vn/game/orecrusher-2</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>orecrusher</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>panic patrol</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/ar/game/panic-patrol
+https://www.crazygames.com/br/game/panic-patrol
+https://www.crazygames.com/cz/game/panic-patrol
+https://www.crazygames.com/de/game/panic-patrol
+https://www.crazygames.com/dk/game/panic-patrol
+https://www.crazygames.com/es/game/panic-patrol
+https://www.crazygames.com/fi/game/panic-patrol
+https://www.crazygames.com/fr/game/panic-patrol
+https://www.crazygames.com/game/panic-patrol
+https://www.crazygames.com/gr/game/panic-patrol
+https://www.crazygames.com/hu/game/panic-patrol
+https://www.crazygames.com/id/game/panic-patrol
+https://www.crazygames.com/it/game/panic-patrol
+https://www.crazygames.com/jp/game/panic-patrol
+https://www.crazygames.com/kr/game/panic-patrol
+https://www.crazygames.com/nl/game/panic-patrol
+https://www.crazygames.com/no/game/panic-patrol
+https://www.crazygames.com/pl/game/panic-patrol
+https://www.crazygames.com/ro/game/panic-patrol
+https://www.crazygames.com/ru/game/panic-patrol
+https://www.crazygames.com/se/game/panic-patrol
+https://www.crazygames.com/th/game/panic-patrol
+https://www.crazygames.com/tr/game/panic-patrol
+https://www.crazygames.com/ua/game/panic-patrol
+https://www.crazygames.com/vn/game/panic-patrol</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="8" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>panic patrol</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>recoil rumble knp</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/ar/game/recoil-rumble-knp
+https://www.crazygames.com/br/game/recoil-rumble-knp
+https://www.crazygames.com/cz/game/recoil-rumble-knp
+https://www.crazygames.com/de/game/recoil-rumble-knp
+https://www.crazygames.com/dk/game/recoil-rumble-knp
+https://www.crazygames.com/es/game/recoil-rumble-knp
+https://www.crazygames.com/fi/game/recoil-rumble-knp
+https://www.crazygames.com/fr/game/recoil-rumble-knp
+https://www.crazygames.com/game/recoil-rumble-knp
+https://www.crazygames.com/gr/game/recoil-rumble-knp
+https://www.crazygames.com/hu/game/recoil-rumble-knp
+https://www.crazygames.com/id/game/recoil-rumble-knp
+https://www.crazygames.com/it/game/recoil-rumble-knp
+https://www.crazygames.com/jp/game/recoil-rumble-knp
+https://www.crazygames.com/kr/game/recoil-rumble-knp
+https://www.crazygames.com/nl/game/recoil-rumble-knp
+https://www.crazygames.com/no/game/recoil-rumble-knp
+https://www.crazygames.com/pl/game/recoil-rumble-knp
+https://www.crazygames.com/ro/game/recoil-rumble-knp
+https://www.crazygames.com/ru/game/recoil-rumble-knp
+https://www.crazygames.com/se/game/recoil-rumble-knp
+https://www.crazygames.com/th/game/recoil-rumble-knp
+https://www.crazygames.com/tr/game/recoil-rumble-knp
+https://www.crazygames.com/ua/game/recoil-rumble-knp
+https://www.crazygames.com/vn/game/recoil-rumble-knp</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="8" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>recoil rumble knp</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/word-monitor-sitemap/report/latest.xlsx
+++ b/word-monitor-sitemap/report/latest.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="keywords" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -470,7 +470,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-07-13T21:37:37</t>
+          <t>2026-07-14T11:55:22</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -540,7 +540,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"inputCount": 9, "requestCount": 9, "successCount": 8, "successWithScoreCount": 8, "missingScoreCount": 0, "failedCount": 1}</t>
+          <t>{"inputCount": 5, "requestCount": 5, "successCount": 5, "successWithScoreCount": 5, "missingScoreCount": 0, "failedCount": 0}</t>
         </is>
       </c>
     </row>
@@ -555,11 +555,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="54" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -637,41 +637,46 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>om nom run</t>
+          <t>voxiom io</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://www.onlinegames.io/om-nom-run</t>
+          <t>https://www.crazygames.com/es/game/voxiom-io
+https://www.crazygames.com/hu/game/voxiom-io
+https://www.crazygames.com/kr/game/voxiom-io
+https://www.crazygames.com/no/game/voxiom-io
+https://www.crazygames.com/pl/game/voxiom-io
+https://www.crazygames.com/tr/game/voxiom-io</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>339.28125</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>13570</v>
+        <v>9870</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.28</v>
+        <v>0.55</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>12830</v>
+        <v>11400</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>60</v>
+        <v>49.5</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>om nom run</t>
+          <t>voxiom io</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -683,41 +688,39 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>jelly run</t>
+          <t>noob archer</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>https://www.onlinegames.io/jelly-run-2048</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>36.625926</v>
-      </c>
+          <t>https://poki.com/en/g/noob-archer-2</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n"/>
       <c r="D3" s="4" t="n">
-        <v>6380</v>
+        <v>120</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>7300</v>
+        <v>500</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>60.5</v>
+        <v>38.3</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>jelly run</t>
+          <t>noob archer</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -729,59 +732,44 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>divine clash</t>
+          <t>merge clash</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/ar/game/divine-clash
-https://www.crazygames.com/br/game/divine-clash
-https://www.crazygames.com/cz/game/divine-clash
-https://www.crazygames.com/de/game/divine-clash
-https://www.crazygames.com/dk/game/divine-clash
-https://www.crazygames.com/es/game/divine-clash
-https://www.crazygames.com/fi/game/divine-clash
-https://www.crazygames.com/fr/game/divine-clash
-https://www.crazygames.com/game/divine-clash
-https://www.crazygames.com/gr/game/divine-clash
-https://www.crazygames.com/hu/game/divine-clash
-https://www.crazygames.com/id/game/divine-clash
-https://www.crazygames.com/it/game/divine-clash
-https://www.crazygames.com/jp/game/divine-clash
-https://www.crazygames.com/kr/game/divine-clash
-https://www.crazygames.com/nl/game/divine-clash
-https://www.crazygames.com/no/game/divine-clash
-https://www.crazygames.com/pl/game/divine-clash
-https://www.crazygames.com/ro/game/divine-clash
-https://www.crazygames.com/ru/game/divine-clash
-https://www.crazygames.com/se/game/divine-clash
-https://www.crazygames.com/th/game/divine-clash
-https://www.crazygames.com/tr/game/divine-clash
-https://www.crazygames.com/ua/game/divine-clash
-https://www.crazygames.com/vn/game/divine-clash</t>
+          <t>https://www.crazygames.com/es/game/merge-clash
+https://www.crazygames.com/hu/game/merge-clash
+https://www.crazygames.com/kr/game/merge-clash
+https://www.crazygames.com/no/game/merge-clash
+https://www.crazygames.com/pl/game/merge-clash
+https://www.crazygames.com/tr/game/merge-clash</t>
         </is>
       </c>
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="4" t="n">
-        <v>1330</v>
+        <v>1570</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0</v>
+        <v>12.29</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="H4" s="7" t="n"/>
-      <c r="I4" s="7" t="n"/>
+        <v>150</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>1.14</v>
+      </c>
       <c r="J4" s="8" t="n">
-        <v>65.5</v>
+        <v>65.2</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>divine clash</t>
+          <t>merge clash</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -793,36 +781,13 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>alphablitz wty</t>
+          <t>fishing anomaly</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/ar/game/alphablitz-wty
-https://www.crazygames.com/br/game/alphablitz-wty
-https://www.crazygames.com/cz/game/alphablitz-wty
-https://www.crazygames.com/de/game/alphablitz-wty
-https://www.crazygames.com/dk/game/alphablitz-wty
-https://www.crazygames.com/es/game/alphablitz-wty
-https://www.crazygames.com/fi/game/alphablitz-wty
-https://www.crazygames.com/fr/game/alphablitz-wty
-https://www.crazygames.com/game/alphablitz-wty
-https://www.crazygames.com/gr/game/alphablitz-wty
-https://www.crazygames.com/hu/game/alphablitz-wty
-https://www.crazygames.com/id/game/alphablitz-wty
-https://www.crazygames.com/it/game/alphablitz-wty
-https://www.crazygames.com/jp/game/alphablitz-wty
-https://www.crazygames.com/kr/game/alphablitz-wty
-https://www.crazygames.com/nl/game/alphablitz-wty
-https://www.crazygames.com/no/game/alphablitz-wty
-https://www.crazygames.com/pl/game/alphablitz-wty
-https://www.crazygames.com/ro/game/alphablitz-wty
-https://www.crazygames.com/ru/game/alphablitz-wty
-https://www.crazygames.com/se/game/alphablitz-wty
-https://www.crazygames.com/th/game/alphablitz-wty
-https://www.crazygames.com/tr/game/alphablitz-wty
-https://www.crazygames.com/ua/game/alphablitz-wty
-https://www.crazygames.com/vn/game/alphablitz-wty</t>
+          <t>https://www.crazygames.com/es/game/fishing-anomaly
+https://www.crazygames.com/hu/game/fishing-anomaly</t>
         </is>
       </c>
       <c r="C5" s="3" t="n"/>
@@ -830,16 +795,18 @@
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
       <c r="J5" s="8" t="n">
-        <v>12.8</v>
+        <v>45.9</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>alphablitz wty</t>
+          <t>fishing anomaly</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -851,271 +818,48 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>farm mayhem merge</t>
+          <t>digworm io</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/ar/game/farm-mayhem-merge
-https://www.crazygames.com/br/game/farm-mayhem-merge
-https://www.crazygames.com/cz/game/farm-mayhem-merge
-https://www.crazygames.com/de/game/farm-mayhem-merge
-https://www.crazygames.com/dk/game/farm-mayhem-merge
-https://www.crazygames.com/es/game/farm-mayhem-merge
-https://www.crazygames.com/fi/game/farm-mayhem-merge
-https://www.crazygames.com/fr/game/farm-mayhem-merge
-https://www.crazygames.com/game/farm-mayhem-merge
-https://www.crazygames.com/gr/game/farm-mayhem-merge
-https://www.crazygames.com/hu/game/farm-mayhem-merge
-https://www.crazygames.com/id/game/farm-mayhem-merge
-https://www.crazygames.com/it/game/farm-mayhem-merge
-https://www.crazygames.com/jp/game/farm-mayhem-merge
-https://www.crazygames.com/kr/game/farm-mayhem-merge
-https://www.crazygames.com/nl/game/farm-mayhem-merge
-https://www.crazygames.com/no/game/farm-mayhem-merge
-https://www.crazygames.com/pl/game/farm-mayhem-merge
-https://www.crazygames.com/ro/game/farm-mayhem-merge
-https://www.crazygames.com/ru/game/farm-mayhem-merge
-https://www.crazygames.com/se/game/farm-mayhem-merge
-https://www.crazygames.com/th/game/farm-mayhem-merge
-https://www.crazygames.com/tr/game/farm-mayhem-merge
-https://www.crazygames.com/ua/game/farm-mayhem-merge
-https://www.crazygames.com/vn/game/farm-mayhem-merge</t>
+          <t>https://www.crazygames.com/es/game/digworm-io
+https://www.crazygames.com/hu/game/digworm-io</t>
         </is>
       </c>
       <c r="C6" s="3" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
+      <c r="D6" s="4" t="n">
+        <v>450</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G6" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
       <c r="J6" s="8" t="n">
-        <v>56.2</v>
+        <v>42.6</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>farm mayhem merge</t>
+          <t>digworm io</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>sem_only（仅 SEM）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>lafufu blind box dress up</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>https://poki.com/en/g/lafufu-blind-box-dress-up</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="8" t="n"/>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>lafufu blind box dress up</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>sem_only（仅 SEM）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>orecrusher</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.crazygames.com/ar/game/orecrusher-2
-https://www.crazygames.com/br/game/orecrusher-2
-https://www.crazygames.com/cz/game/orecrusher-2
-https://www.crazygames.com/de/game/orecrusher-2
-https://www.crazygames.com/dk/game/orecrusher-2
-https://www.crazygames.com/es/game/orecrusher-2
-https://www.crazygames.com/fi/game/orecrusher-2
-https://www.crazygames.com/fr/game/orecrusher-2
-https://www.crazygames.com/game/orecrusher-2
-https://www.crazygames.com/gr/game/orecrusher-2
-https://www.crazygames.com/hu/game/orecrusher-2
-https://www.crazygames.com/id/game/orecrusher-2
-https://www.crazygames.com/it/game/orecrusher-2
-https://www.crazygames.com/jp/game/orecrusher-2
-https://www.crazygames.com/kr/game/orecrusher-2
-https://www.crazygames.com/nl/game/orecrusher-2
-https://www.crazygames.com/no/game/orecrusher-2
-https://www.crazygames.com/pl/game/orecrusher-2
-https://www.crazygames.com/ro/game/orecrusher-2
-https://www.crazygames.com/ru/game/orecrusher-2
-https://www.crazygames.com/se/game/orecrusher-2
-https://www.crazygames.com/th/game/orecrusher-2
-https://www.crazygames.com/tr/game/orecrusher-2
-https://www.crazygames.com/ua/game/orecrusher-2
-https://www.crazygames.com/vn/game/orecrusher-2</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="8" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>orecrusher</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>sem_only（仅 SEM）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>panic patrol</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.crazygames.com/ar/game/panic-patrol
-https://www.crazygames.com/br/game/panic-patrol
-https://www.crazygames.com/cz/game/panic-patrol
-https://www.crazygames.com/de/game/panic-patrol
-https://www.crazygames.com/dk/game/panic-patrol
-https://www.crazygames.com/es/game/panic-patrol
-https://www.crazygames.com/fi/game/panic-patrol
-https://www.crazygames.com/fr/game/panic-patrol
-https://www.crazygames.com/game/panic-patrol
-https://www.crazygames.com/gr/game/panic-patrol
-https://www.crazygames.com/hu/game/panic-patrol
-https://www.crazygames.com/id/game/panic-patrol
-https://www.crazygames.com/it/game/panic-patrol
-https://www.crazygames.com/jp/game/panic-patrol
-https://www.crazygames.com/kr/game/panic-patrol
-https://www.crazygames.com/nl/game/panic-patrol
-https://www.crazygames.com/no/game/panic-patrol
-https://www.crazygames.com/pl/game/panic-patrol
-https://www.crazygames.com/ro/game/panic-patrol
-https://www.crazygames.com/ru/game/panic-patrol
-https://www.crazygames.com/se/game/panic-patrol
-https://www.crazygames.com/th/game/panic-patrol
-https://www.crazygames.com/tr/game/panic-patrol
-https://www.crazygames.com/ua/game/panic-patrol
-https://www.crazygames.com/vn/game/panic-patrol</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="7" t="n"/>
-      <c r="J9" s="8" t="n">
-        <v>67.09999999999999</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>panic patrol</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>sem_only（仅 SEM）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>recoil rumble knp</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.crazygames.com/ar/game/recoil-rumble-knp
-https://www.crazygames.com/br/game/recoil-rumble-knp
-https://www.crazygames.com/cz/game/recoil-rumble-knp
-https://www.crazygames.com/de/game/recoil-rumble-knp
-https://www.crazygames.com/dk/game/recoil-rumble-knp
-https://www.crazygames.com/es/game/recoil-rumble-knp
-https://www.crazygames.com/fi/game/recoil-rumble-knp
-https://www.crazygames.com/fr/game/recoil-rumble-knp
-https://www.crazygames.com/game/recoil-rumble-knp
-https://www.crazygames.com/gr/game/recoil-rumble-knp
-https://www.crazygames.com/hu/game/recoil-rumble-knp
-https://www.crazygames.com/id/game/recoil-rumble-knp
-https://www.crazygames.com/it/game/recoil-rumble-knp
-https://www.crazygames.com/jp/game/recoil-rumble-knp
-https://www.crazygames.com/kr/game/recoil-rumble-knp
-https://www.crazygames.com/nl/game/recoil-rumble-knp
-https://www.crazygames.com/no/game/recoil-rumble-knp
-https://www.crazygames.com/pl/game/recoil-rumble-knp
-https://www.crazygames.com/ro/game/recoil-rumble-knp
-https://www.crazygames.com/ru/game/recoil-rumble-knp
-https://www.crazygames.com/se/game/recoil-rumble-knp
-https://www.crazygames.com/th/game/recoil-rumble-knp
-https://www.crazygames.com/tr/game/recoil-rumble-knp
-https://www.crazygames.com/ua/game/recoil-rumble-knp
-https://www.crazygames.com/vn/game/recoil-rumble-knp</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="7" t="n"/>
-      <c r="I10" s="7" t="n"/>
-      <c r="J10" s="8" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>recoil rumble knp</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>sem_only（仅 SEM）</t>
+          <t>both（SIM+SEM）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L10"/>
+  <autoFilter ref="A1:L6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/word-monitor-sitemap/report/latest.xlsx
+++ b/word-monitor-sitemap/report/latest.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="keywords" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -470,7 +470,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-07-14T11:55:22</t>
+          <t>2026-07-15T19:52:18</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -540,7 +540,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"inputCount": 5, "requestCount": 5, "successCount": 5, "successWithScoreCount": 5, "missingScoreCount": 0, "failedCount": 0}</t>
+          <t>{"inputCount": 6, "requestCount": 6, "successCount": 6, "successWithScoreCount": 6, "missingScoreCount": 0, "failedCount": 0}</t>
         </is>
       </c>
     </row>
@@ -555,11 +555,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -637,90 +637,89 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>voxiom io</t>
+          <t>chicken hell</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/es/game/voxiom-io
-https://www.crazygames.com/hu/game/voxiom-io
-https://www.crazygames.com/kr/game/voxiom-io
-https://www.crazygames.com/no/game/voxiom-io
-https://www.crazygames.com/pl/game/voxiom-io
-https://www.crazygames.com/tr/game/voxiom-io</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>339.28125</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>9870</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>0.55</v>
-      </c>
+          <t>https://www.crazygames.com/ar/game/chicken-hell
+https://www.crazygames.com/br/game/chicken-hell
+https://www.crazygames.com/cz/game/chicken-hell
+https://www.crazygames.com/de/game/chicken-hell
+https://www.crazygames.com/fi/game/chicken-hell
+https://www.crazygames.com/gr/game/chicken-hell
+https://www.crazygames.com/pl/game/chicken-hell
+https://www.crazygames.com/ru/game/chicken-hell
+https://www.crazygames.com/se/game/chicken-hell
+https://www.crazygames.com/th/game/chicken-hell
+https://www.crazygames.com/tr/game/chicken-hell
+https://www.crazygames.com/ua/game/chicken-hell</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
       <c r="G2" s="6" t="n">
-        <v>11400</v>
-      </c>
-      <c r="H2" s="7" t="n">
-        <v>39</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="H2" s="7" t="n"/>
       <c r="I2" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>49.5</v>
+        <v>28.8</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>voxiom io</t>
+          <t>chicken hell</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>both（SIM+SEM）</t>
+          <t>sem_only（仅 SEM）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>noob archer</t>
+          <t>zombie lab escape</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>https://poki.com/en/g/noob-archer-2</t>
+          <t>https://www.crazygames.com/es/game/zombie-lab-escape
+https://www.crazygames.com/fr/game/zombie-lab-escape
+https://www.crazygames.com/game/zombie-lab-escape
+https://www.crazygames.com/hu/game/zombie-lab-escape
+https://www.crazygames.com/id/game/zombie-lab-escape
+https://www.crazygames.com/jp/game/zombie-lab-escape
+https://www.crazygames.com/kr/game/zombie-lab-escape
+https://www.crazygames.com/no/game/zombie-lab-escape</t>
         </is>
       </c>
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="4" t="n">
-        <v>120</v>
+        <v>430</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>500</v>
-      </c>
-      <c r="H3" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="I3" s="7" t="n">
-        <v>0.11</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H3" s="7" t="n"/>
+      <c r="I3" s="7" t="n"/>
       <c r="J3" s="8" t="n">
-        <v>38.3</v>
+        <v>23.5</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>noob archer</t>
+          <t>zombie lab escape</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -732,62 +731,48 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>merge clash</t>
+          <t>craft 4eva</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/es/game/merge-clash
-https://www.crazygames.com/hu/game/merge-clash
-https://www.crazygames.com/kr/game/merge-clash
-https://www.crazygames.com/no/game/merge-clash
-https://www.crazygames.com/pl/game/merge-clash
-https://www.crazygames.com/tr/game/merge-clash</t>
+          <t>https://www.crazygames.com/no/game/craft-4eva</t>
         </is>
       </c>
       <c r="C4" s="3" t="n"/>
-      <c r="D4" s="4" t="n">
-        <v>1570</v>
-      </c>
-      <c r="E4" s="5" t="n">
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="5" t="n">
-        <v>12.29</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>150</v>
-      </c>
-      <c r="H4" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>1.14</v>
-      </c>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
       <c r="J4" s="8" t="n">
-        <v>65.2</v>
+        <v>17.5</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>merge clash</t>
+          <t>craft 4eva</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>both（SIM+SEM）</t>
+          <t>sem_only（仅 SEM）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>fishing anomaly</t>
+          <t>escape from school runaway</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/es/game/fishing-anomaly
-https://www.crazygames.com/hu/game/fishing-anomaly</t>
+          <t>https://www.crazygames.com/fr/game/escape-from-school-runaway
+https://www.crazygames.com/hu/game/escape-from-school-runaway
+https://www.crazygames.com/no/game/escape-from-school-runaway</t>
         </is>
       </c>
       <c r="C5" s="3" t="n"/>
@@ -795,18 +780,18 @@
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="6" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>45.9</v>
+        <v>39.5</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>fishing anomaly</t>
+          <t>escape from school runaway</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -818,48 +803,73 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>digworm io</t>
+          <t>home makeover cleaning game</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/es/game/digworm-io
-https://www.crazygames.com/hu/game/digworm-io</t>
+          <t>https://www.crazygames.com/no/game/home-makeover-cleaning-game</t>
         </is>
       </c>
       <c r="C6" s="3" t="n"/>
-      <c r="D6" s="4" t="n">
-        <v>450</v>
-      </c>
-      <c r="E6" s="5" t="n">
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="8" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>home makeover cleaning game</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>strange mazes</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/no/game/strange-mazes</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="8" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>digworm io</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>both（SIM+SEM）</t>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
+      <c r="J7" s="8" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>strange mazes</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L6"/>
+  <autoFilter ref="A1:L7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/word-monitor-sitemap/report/latest.xlsx
+++ b/word-monitor-sitemap/report/latest.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="keywords" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -470,7 +470,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-07-15T19:52:18</t>
+          <t>2026-07-16T13:41:05</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -540,7 +540,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"inputCount": 6, "requestCount": 6, "successCount": 6, "successWithScoreCount": 6, "missingScoreCount": 0, "failedCount": 0}</t>
+          <t>{"inputCount": 12, "requestCount": 12, "successCount": 12, "successWithScoreCount": 12, "missingScoreCount": 0, "failedCount": 0}</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -637,106 +637,108 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>chicken hell</t>
+          <t>smashing bottles</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/ar/game/chicken-hell
-https://www.crazygames.com/br/game/chicken-hell
-https://www.crazygames.com/cz/game/chicken-hell
-https://www.crazygames.com/de/game/chicken-hell
-https://www.crazygames.com/fi/game/chicken-hell
-https://www.crazygames.com/gr/game/chicken-hell
-https://www.crazygames.com/pl/game/chicken-hell
-https://www.crazygames.com/ru/game/chicken-hell
-https://www.crazygames.com/se/game/chicken-hell
-https://www.crazygames.com/th/game/chicken-hell
-https://www.crazygames.com/tr/game/chicken-hell
-https://www.crazygames.com/ua/game/chicken-hell</t>
+          <t>https://www.crazygames.com/cz/game/smashing-bottles
+https://www.crazygames.com/gr/game/smashing-bottles
+https://www.crazygames.com/pl/game/smashing-bottles
+https://www.crazygames.com/ru/game/smashing-bottles
+https://www.crazygames.com/se/game/smashing-bottles
+https://www.crazygames.com/tr/game/smashing-bottles
+https://www.crazygames.com/ua/game/smashing-bottles</t>
         </is>
       </c>
       <c r="C2" s="3" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="5" t="n"/>
-      <c r="F2" s="5" t="n"/>
+      <c r="D2" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G2" s="6" t="n">
-        <v>280</v>
+        <v>600</v>
       </c>
       <c r="H2" s="7" t="n"/>
       <c r="I2" s="7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>28.8</v>
+        <v>37.8</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>chicken hell</t>
+          <t>smashing bottles</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>sem_only（仅 SEM）</t>
+          <t>both（SIM+SEM）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>zombie lab escape</t>
+          <t>chicken hell</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/es/game/zombie-lab-escape
-https://www.crazygames.com/fr/game/zombie-lab-escape
-https://www.crazygames.com/game/zombie-lab-escape
-https://www.crazygames.com/hu/game/zombie-lab-escape
-https://www.crazygames.com/id/game/zombie-lab-escape
-https://www.crazygames.com/jp/game/zombie-lab-escape
-https://www.crazygames.com/kr/game/zombie-lab-escape
-https://www.crazygames.com/no/game/zombie-lab-escape</t>
+          <t>https://www.crazygames.com/dk/game/chicken-hell
+https://www.crazygames.com/es/game/chicken-hell
+https://www.crazygames.com/fr/game/chicken-hell
+https://www.crazygames.com/game/chicken-hell
+https://www.crazygames.com/hu/game/chicken-hell
+https://www.crazygames.com/id/game/chicken-hell
+https://www.crazygames.com/it/game/chicken-hell
+https://www.crazygames.com/jp/game/chicken-hell
+https://www.crazygames.com/kr/game/chicken-hell
+https://www.crazygames.com/nl/game/chicken-hell
+https://www.crazygames.com/no/game/chicken-hell
+https://www.crazygames.com/ro/game/chicken-hell
+https://www.crazygames.com/vn/game/chicken-hell</t>
         </is>
       </c>
       <c r="C3" s="3" t="n"/>
-      <c r="D3" s="4" t="n">
-        <v>430</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="H3" s="7" t="n"/>
-      <c r="I3" s="7" t="n"/>
+      <c r="I3" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="J3" s="8" t="n">
-        <v>23.5</v>
+        <v>28.8</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>zombie lab escape</t>
+          <t>chicken hell</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>both（SIM+SEM）</t>
+          <t>sem_only（仅 SEM）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>craft 4eva</t>
+          <t>ai video from text and url</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/no/game/craft-4eva</t>
+          <t>https://higgsfield.ai/blog/ai-video-from-text-and-url</t>
         </is>
       </c>
       <c r="C4" s="3" t="n"/>
@@ -749,11 +751,11 @@
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
       <c r="J4" s="8" t="n">
-        <v>17.5</v>
+        <v>36.2</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>craft 4eva</t>
+          <t>ai video from text and url</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -765,14 +767,18 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>escape from school runaway</t>
+          <t>carrom stars io</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/fr/game/escape-from-school-runaway
-https://www.crazygames.com/hu/game/escape-from-school-runaway
-https://www.crazygames.com/no/game/escape-from-school-runaway</t>
+          <t>https://www.crazygames.com/cz/game/carrom-stars-io
+https://www.crazygames.com/gr/game/carrom-stars-io
+https://www.crazygames.com/pl/game/carrom-stars-io
+https://www.crazygames.com/ru/game/carrom-stars-io
+https://www.crazygames.com/se/game/carrom-stars-io
+https://www.crazygames.com/tr/game/carrom-stars-io
+https://www.crazygames.com/ua/game/carrom-stars-io</t>
         </is>
       </c>
       <c r="C5" s="3" t="n"/>
@@ -783,15 +789,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="I5" s="7" t="n"/>
       <c r="J5" s="8" t="n">
-        <v>39.5</v>
+        <v>37.6</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>escape from school runaway</t>
+          <t>carrom stars io</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -803,12 +807,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>home makeover cleaning game</t>
+          <t>cinema studio full tutorial</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/no/game/home-makeover-cleaning-game</t>
+          <t>https://higgsfield.ai/blog/cinema-studio-3.5-full-tutorial</t>
         </is>
       </c>
       <c r="C6" s="3" t="n"/>
@@ -821,11 +825,11 @@
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
       <c r="J6" s="8" t="n">
-        <v>35.1</v>
+        <v>43</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>home makeover cleaning game</t>
+          <t>cinema studio full tutorial</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -837,12 +841,18 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>strange mazes</t>
+          <t>drone delivery chaos fkw</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/no/game/strange-mazes</t>
+          <t>https://www.crazygames.com/cz/game/drone-delivery-chaos-fkw
+https://www.crazygames.com/gr/game/drone-delivery-chaos-fkw
+https://www.crazygames.com/pl/game/drone-delivery-chaos-fkw
+https://www.crazygames.com/ru/game/drone-delivery-chaos-fkw
+https://www.crazygames.com/se/game/drone-delivery-chaos-fkw
+https://www.crazygames.com/tr/game/drone-delivery-chaos-fkw
+https://www.crazygames.com/ua/game/drone-delivery-chaos-fkw</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -855,11 +865,11 @@
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
       <c r="J7" s="8" t="n">
-        <v>18.2</v>
+        <v>23.6</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>strange mazes</t>
+          <t>drone delivery chaos fkw</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -868,8 +878,225 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>how to play lows adventures</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.coolmathgames.com/blog/how-to-play-lows-adventures</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>how to play lows adventures</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>idle car service tycoon</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/cz/game/idle-car-service-tycoon
+https://www.crazygames.com/gr/game/idle-car-service-tycoon
+https://www.crazygames.com/se/game/idle-car-service-tycoon
+https://www.crazygames.com/tr/game/idle-car-service-tycoon</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="8" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>idle car service tycoon</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>one of one studio interview</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>https://higgsfield.ai/blog/one-of-one-studio-interview</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="8" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>one of one studio interview</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>sandbox of elements</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>https://poki.com/en/g/sandbox-of-elements</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
+      <c r="J11" s="8" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>sandbox of elements</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>waddle quest</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/cz/game/waddle-s-quest
+https://www.crazygames.com/gr/game/waddle-s-quest
+https://www.crazygames.com/se/game/waddle-s-quest
+https://www.crazygames.com/tr/game/waddle-s-quest</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="8" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>waddle quest</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>whatisthismovie</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>https://huntifyai.com/tools/whatisthismovie
+https://huntifyai.com/zh-CN/tools/whatisthismovie</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="7" t="n"/>
+      <c r="J13" s="8" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>whatisthismovie</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L7"/>
+  <autoFilter ref="A1:L13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/word-monitor-sitemap/report/latest.xlsx
+++ b/word-monitor-sitemap/report/latest.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="keywords" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -470,7 +470,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-07-16T13:41:05</t>
+          <t>2026-07-21T17:07:36</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -540,7 +540,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"inputCount": 12, "requestCount": 12, "successCount": 12, "successWithScoreCount": 12, "missingScoreCount": 0, "failedCount": 0}</t>
+          <t>{"inputCount": 30, "requestCount": 30, "successCount": 30, "successWithScoreCount": 30, "missingScoreCount": 0, "failedCount": 0}</t>
         </is>
       </c>
     </row>
@@ -555,10 +555,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="1" max="1"/>
     <col width="64" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -568,7 +568,7 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="93" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -637,43 +637,39 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>smashing bottles</t>
+          <t>unmatched ego</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/cz/game/smashing-bottles
-https://www.crazygames.com/gr/game/smashing-bottles
-https://www.crazygames.com/pl/game/smashing-bottles
-https://www.crazygames.com/ru/game/smashing-bottles
-https://www.crazygames.com/se/game/smashing-bottles
-https://www.crazygames.com/tr/game/smashing-bottles
-https://www.crazygames.com/ua/game/smashing-bottles</t>
+          <t>https://www.crazygames.com/cz/game/unmatched-ego-2</t>
         </is>
       </c>
       <c r="C2" s="3" t="n"/>
       <c r="D2" s="4" t="n">
-        <v>30</v>
+        <v>14220</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>600</v>
-      </c>
-      <c r="H2" s="7" t="n"/>
+        <v>14960</v>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>18</v>
+      </c>
       <c r="I2" s="7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>37.8</v>
+        <v>52</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>smashing bottles</t>
+          <t>unmatched ego</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -685,24 +681,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>chicken hell</t>
+          <t>tranai</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/dk/game/chicken-hell
-https://www.crazygames.com/es/game/chicken-hell
-https://www.crazygames.com/fr/game/chicken-hell
-https://www.crazygames.com/game/chicken-hell
-https://www.crazygames.com/hu/game/chicken-hell
-https://www.crazygames.com/id/game/chicken-hell
-https://www.crazygames.com/it/game/chicken-hell
-https://www.crazygames.com/jp/game/chicken-hell
-https://www.crazygames.com/kr/game/chicken-hell
-https://www.crazygames.com/nl/game/chicken-hell
-https://www.crazygames.com/no/game/chicken-hell
-https://www.crazygames.com/ro/game/chicken-hell
-https://www.crazygames.com/vn/game/chicken-hell</t>
+          <t>https://huntifyai.com/zh-CN/tools/tranai</t>
         </is>
       </c>
       <c r="C3" s="3" t="n"/>
@@ -710,18 +694,18 @@
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="H3" s="7" t="n"/>
       <c r="I3" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>28.8</v>
+        <v>25.4</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>chicken hell</t>
+          <t>tranai</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -733,52 +717,56 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ai video from text and url</t>
+          <t>script to storyboard ai</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://higgsfield.ai/blog/ai-video-from-text-and-url</t>
+          <t>https://higgsfield.ai/blog/script-to-storyboard-ai</t>
         </is>
       </c>
       <c r="C4" s="3" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
+      <c r="D4" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>4.49</v>
+      </c>
       <c r="G4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="7" t="n"/>
-      <c r="I4" s="7" t="n"/>
+        <v>200</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>2.4</v>
+      </c>
       <c r="J4" s="8" t="n">
-        <v>36.2</v>
+        <v>42.1</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>ai video from text and url</t>
+          <t>script to storyboard ai</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>sem_only（仅 SEM）</t>
+          <t>both（SIM+SEM）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>carrom stars io</t>
+          <t>catch pet</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/cz/game/carrom-stars-io
-https://www.crazygames.com/gr/game/carrom-stars-io
-https://www.crazygames.com/pl/game/carrom-stars-io
-https://www.crazygames.com/ru/game/carrom-stars-io
-https://www.crazygames.com/se/game/carrom-stars-io
-https://www.crazygames.com/tr/game/carrom-stars-io
-https://www.crazygames.com/ua/game/carrom-stars-io</t>
+          <t>https://poki.com/en/g/catch-a-pet</t>
         </is>
       </c>
       <c r="C5" s="3" t="n"/>
@@ -786,16 +774,18 @@
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="6" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
+      <c r="I5" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="J5" s="8" t="n">
-        <v>37.6</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>carrom stars io</t>
+          <t>catch pet</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -807,52 +797,58 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>cinema studio full tutorial</t>
+          <t>triple3d</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://higgsfield.ai/blog/cinema-studio-3.5-full-tutorial</t>
+          <t>https://huntifyai.com/tools/triple3d
+https://huntifyai.com/zh-CN/tools/triple3d</t>
         </is>
       </c>
       <c r="C6" s="3" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
+      <c r="D6" s="4" t="n">
+        <v>540</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
+        <v>160</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>0.76</v>
+      </c>
       <c r="J6" s="8" t="n">
-        <v>43</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>cinema studio full tutorial</t>
+          <t>triple3d</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>sem_only（仅 SEM）</t>
+          <t>both（SIM+SEM）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>drone delivery chaos fkw</t>
+          <t>creator partnership program</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/cz/game/drone-delivery-chaos-fkw
-https://www.crazygames.com/gr/game/drone-delivery-chaos-fkw
-https://www.crazygames.com/pl/game/drone-delivery-chaos-fkw
-https://www.crazygames.com/ru/game/drone-delivery-chaos-fkw
-https://www.crazygames.com/se/game/drone-delivery-chaos-fkw
-https://www.crazygames.com/tr/game/drone-delivery-chaos-fkw
-https://www.crazygames.com/ua/game/drone-delivery-chaos-fkw</t>
+          <t>https://higgsfield.ai/blog/creator-partnership-program
+https://higgsfield.ai/creator-partnership-program</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -860,16 +856,18 @@
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
+      <c r="I7" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="J7" s="8" t="n">
-        <v>23.6</v>
+        <v>15</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>drone delivery chaos fkw</t>
+          <t>creator partnership program</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -881,12 +879,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>how to play lows adventures</t>
+          <t>how to make creative ads</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>https://www.coolmathgames.com/blog/how-to-play-lows-adventures</t>
+          <t>https://higgsfield.ai/blog/how-to-make-100-creative-ads</t>
         </is>
       </c>
       <c r="C8" s="3" t="n"/>
@@ -894,16 +892,18 @@
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="6" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="n"/>
+      <c r="I8" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="J8" s="8" t="n">
-        <v>16.6</v>
+        <v>47</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>how to play lows adventures</t>
+          <t>how to make creative ads</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -915,49 +915,55 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>idle car service tycoon</t>
+          <t>codeproxy</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/cz/game/idle-car-service-tycoon
-https://www.crazygames.com/gr/game/idle-car-service-tycoon
-https://www.crazygames.com/se/game/idle-car-service-tycoon
-https://www.crazygames.com/tr/game/idle-car-service-tycoon</t>
+          <t>https://huntifyai.com/tools/codeproxy
+https://huntifyai.com/zh-CN/tools/codeproxy</t>
         </is>
       </c>
       <c r="C9" s="3" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="D9" s="4" t="n">
+        <v>380</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="7" t="n"/>
-      <c r="I9" s="7" t="n"/>
+      <c r="I9" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="J9" s="8" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>idle car service tycoon</t>
+          <t>codeproxy</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>sem_only（仅 SEM）</t>
+          <t>both（SIM+SEM）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>one of one studio interview</t>
+          <t>ai previsualization tools</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>https://higgsfield.ai/blog/one-of-one-studio-interview</t>
+          <t>https://higgsfield.ai/blog/ai-previsualization-tools</t>
         </is>
       </c>
       <c r="C10" s="3" t="n"/>
@@ -970,11 +976,11 @@
       <c r="H10" s="7" t="n"/>
       <c r="I10" s="7" t="n"/>
       <c r="J10" s="8" t="n">
-        <v>29.7</v>
+        <v>19.8</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>one of one studio interview</t>
+          <t>ai previsualization tools</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -986,55 +992,47 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>sandbox of elements</t>
+          <t>app builder breakdown</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>https://poki.com/en/g/sandbox-of-elements</t>
+          <t>https://higgsfield.ai/blog/app-builder-breakdown</t>
         </is>
       </c>
       <c r="C11" s="3" t="n"/>
-      <c r="D11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
       <c r="G11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="7" t="n"/>
       <c r="I11" s="7" t="n"/>
       <c r="J11" s="8" t="n">
-        <v>37.2</v>
+        <v>29.2</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>sandbox of elements</t>
+          <t>app builder breakdown</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>both（SIM+SEM）</t>
+          <t>sem_only（仅 SEM）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>waddle quest</t>
+          <t>brainrotkit</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/cz/game/waddle-s-quest
-https://www.crazygames.com/gr/game/waddle-s-quest
-https://www.crazygames.com/se/game/waddle-s-quest
-https://www.crazygames.com/tr/game/waddle-s-quest</t>
+          <t>https://huntifyai.com/tools/brainrotkit
+https://huntifyai.com/zh-CN/tools/brainrotkit</t>
         </is>
       </c>
       <c r="C12" s="3" t="n"/>
@@ -1047,11 +1045,11 @@
       <c r="H12" s="7" t="n"/>
       <c r="I12" s="7" t="n"/>
       <c r="J12" s="8" t="n">
-        <v>34.5</v>
+        <v>38.4</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>waddle quest</t>
+          <t>brainrotkit</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1063,13 +1061,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>whatisthismovie</t>
+          <t>business keywords list for seo marketing and lead generation</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>https://huntifyai.com/tools/whatisthismovie
-https://huntifyai.com/zh-CN/tools/whatisthismovie</t>
+          <t>https://dragganaitool.com/business-keywords-list-for-seo-marketing-and-lead-generation</t>
         </is>
       </c>
       <c r="C13" s="3" t="n"/>
@@ -1082,11 +1079,11 @@
       <c r="H13" s="7" t="n"/>
       <c r="I13" s="7" t="n"/>
       <c r="J13" s="8" t="n">
-        <v>16.9</v>
+        <v>17.4</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>whatisthismovie</t>
+          <t>business keywords list for seo marketing and lead generation</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1095,8 +1092,620 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>case4k</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>https://higgsfield.ai/blog/case4k</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>case4k</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce job title taxonomy how to classify ecommerce roles</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>https://dragganaitool.com/ecommerce-job-title-taxonomy-how-to-classify-ecommerce-roles</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="8" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce job title taxonomy how to classify ecommerce roles</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>gzyi top</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>https://huntifyai.com/zh-CN/tools/gzyi-top</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="7" t="n"/>
+      <c r="J16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>gzyi top</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>how to avoid distortions ai videos</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>https://higgsfield.ai/blog/how-to-avoid-distortions-ai-videos</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="7" t="n"/>
+      <c r="I17" s="7" t="n"/>
+      <c r="J17" s="8" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>how to avoid distortions ai videos</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>key features every user friendly online shopping website should include</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>https://dragganaitool.com/key-features-every-user-friendly-online-shopping-website-should-include</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="7" t="n"/>
+      <c r="I18" s="7" t="n"/>
+      <c r="J18" s="8" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>key features every user friendly online shopping website should include</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>make creative ads</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>https://higgsfield.ai/blog/make-100-creative-ads</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="7" t="n"/>
+      <c r="J19" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>make creative ads</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>planograms explained retail shelf planning best practices</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>https://dragganaitool.com/planograms-explained-retail-shelf-planning-best-practices</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="7" t="n"/>
+      <c r="I20" s="7" t="n"/>
+      <c r="J20" s="8" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>planograms explained retail shelf planning best practices</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ragdoll chaos</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>https://poki.com/en/g/ragdoll-chaos</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="7" t="n"/>
+      <c r="I21" s="7" t="n"/>
+      <c r="J21" s="8" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>ragdoll chaos</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>remittance processing how payment processing systems work</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>https://dragganaitool.com/remittance-processing-how-payment-processing-systems-work</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="7" t="n"/>
+      <c r="I22" s="7" t="n"/>
+      <c r="J22" s="8" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>remittance processing how payment processing systems work</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>scratch card kingdom ufr</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/cz/game/scratch-card-kingdom-ufr</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="7" t="n"/>
+      <c r="I23" s="7" t="n"/>
+      <c r="J23" s="8" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>scratch card kingdom ufr</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>sge snippets explained ai search seo impact</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>https://dragganaitool.com/sge-snippets-explained-ai-search-seo-impact</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="7" t="n"/>
+      <c r="I24" s="7" t="n"/>
+      <c r="J24" s="8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>sge snippets explained ai search seo impact</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>sole proprietorship advantages and disadvantages explained</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>https://dragganaitool.com/sole-proprietorship-advantages-and-disadvantages-explained</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="7" t="n"/>
+      <c r="I25" s="7" t="n"/>
+      <c r="J25" s="8" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>sole proprietorship advantages and disadvantages explained</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>task priority levels explained high medium low urgent and popular prioritization frameworks</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>https://dragganaitool.com/task-priority-levels-explained-high-medium-low-urgent-and-popular-prioritization-frameworks</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="7" t="n"/>
+      <c r="I26" s="7" t="n"/>
+      <c r="J26" s="8" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>task priority levels explained high medium low urgent and popular prioritization frameworks</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>tax filing tools that help you save time and maximize deductions</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>https://dragganaitool.com/tax-filing-tools-that-help-you-save-time-and-maximize-deductions</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="7" t="n"/>
+      <c r="I27" s="7" t="n"/>
+      <c r="J27" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>tax filing tools that help you save time and maximize deductions</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>top ecommerce podcasts every online seller should listen to</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>https://dragganaitool.com/top-6-ecommerce-podcasts-every-online-seller-should-listen-to-2026</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="7" t="n"/>
+      <c r="I28" s="7" t="n"/>
+      <c r="J28" s="8" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>top ecommerce podcasts every online seller should listen to</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>top retail competitor pricing data tools</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>https://dragganaitool.com/top-7-retail-competitor-pricing-data-tools-2026</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="7" t="n"/>
+      <c r="I29" s="7" t="n"/>
+      <c r="J29" s="8" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>top retail competitor pricing data tools</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>top wcag testing tools for website owners</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>https://dragganaitool.com/top-5-wcag-testing-tools-for-website-owners</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="7" t="n"/>
+      <c r="I30" s="7" t="n"/>
+      <c r="J30" s="8" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>top wcag testing tools for website owners</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>what is category name definition examples</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>https://dragganaitool.com/what-is-a-category-name-definition-examples</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="7" t="n"/>
+      <c r="I31" s="7" t="n"/>
+      <c r="J31" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>what is category name definition examples</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L13"/>
+  <autoFilter ref="A1:L31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/word-monitor-sitemap/report/latest.xlsx
+++ b/word-monitor-sitemap/report/latest.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="keywords" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -470,7 +470,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-07-21T17:07:36</t>
+          <t>2026-07-22T17:46:59</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -540,7 +540,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"inputCount": 30, "requestCount": 30, "successCount": 30, "successWithScoreCount": 30, "missingScoreCount": 0, "failedCount": 0}</t>
+          <t>{"inputCount": 39, "requestCount": 39, "successCount": 39, "successWithScoreCount": 39, "missingScoreCount": 0, "failedCount": 0}</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -642,7 +642,13 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/cz/game/unmatched-ego-2</t>
+          <t>https://www.crazygames.com/ar/game/unmatched-ego-2
+https://www.crazygames.com/br/game/unmatched-ego-2
+https://www.crazygames.com/fr/game/unmatched-ego-2
+https://www.crazygames.com/pl/game/unmatched-ego-2
+https://www.crazygames.com/ro/game/unmatched-ego-2
+https://www.crazygames.com/se/game/unmatched-ego-2
+https://www.crazygames.com/th/game/unmatched-ego-2</t>
         </is>
       </c>
       <c r="C2" s="3" t="n"/>
@@ -761,12 +767,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>catch pet</t>
+          <t>poppy strike</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>https://poki.com/en/g/catch-a-pet</t>
+          <t>https://www.onlinegames.io/poppy-strike-5</t>
         </is>
       </c>
       <c r="C5" s="3" t="n"/>
@@ -774,18 +780,18 @@
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="6" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>69.90000000000001</v>
+        <v>44.1</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>catch pet</t>
+          <t>poppy strike</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -797,94 +803,93 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>catch pet</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://poki.com/en/g/catch-a-pet</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>catch pet</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>triple3d</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>https://huntifyai.com/tools/triple3d
 https://huntifyai.com/zh-CN/tools/triple3d</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="4" t="n">
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="4" t="n">
         <v>540</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E7" s="5" t="n">
         <v>81</v>
       </c>
-      <c r="F6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="6" t="n">
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="H7" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="I7" s="7" t="n">
         <v>0.76</v>
       </c>
-      <c r="J6" s="8" t="n">
+      <c r="J7" s="8" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>triple3d</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>both（SIM+SEM）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>creator partnership program</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>https://higgsfield.ai/blog/creator-partnership-program
-https://higgsfield.ai/creator-partnership-program</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>creator partnership program</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>sem_only（仅 SEM）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>how to make creative ads</t>
+          <t>world war shooter</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>https://higgsfield.ai/blog/how-to-make-100-creative-ads</t>
+          <t>https://www.onlinegames.io/world-war-2-shooter</t>
         </is>
       </c>
       <c r="C8" s="3" t="n"/>
@@ -892,18 +897,18 @@
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="6" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="H8" s="7" t="n"/>
       <c r="I8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>47</v>
+        <v>36.4</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>how to make creative ads</t>
+          <t>world war shooter</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -915,55 +920,49 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>codeproxy</t>
+          <t>creator partnership program</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>https://huntifyai.com/tools/codeproxy
-https://huntifyai.com/zh-CN/tools/codeproxy</t>
+          <t>https://higgsfield.ai/blog/creator-partnership-program
+https://higgsfield.ai/creator-partnership-program</t>
         </is>
       </c>
       <c r="C9" s="3" t="n"/>
-      <c r="D9" s="4" t="n">
-        <v>380</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
       <c r="G9" s="6" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H9" s="7" t="n"/>
       <c r="I9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>39.2</v>
+        <v>15</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>codeproxy</t>
+          <t>creator partnership program</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>both（SIM+SEM）</t>
+          <t>sem_only（仅 SEM）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ai previsualization tools</t>
+          <t>how to make creative ads</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>https://higgsfield.ai/blog/ai-previsualization-tools</t>
+          <t>https://higgsfield.ai/blog/how-to-make-100-creative-ads</t>
         </is>
       </c>
       <c r="C10" s="3" t="n"/>
@@ -971,16 +970,18 @@
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="6" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H10" s="7" t="n"/>
-      <c r="I10" s="7" t="n"/>
+      <c r="I10" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="J10" s="8" t="n">
-        <v>19.8</v>
+        <v>47</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>ai previsualization tools</t>
+          <t>how to make creative ads</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -992,115 +993,165 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>app builder breakdown</t>
+          <t>putt day</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>https://higgsfield.ai/blog/app-builder-breakdown</t>
+          <t>https://www.crazygames.com/ar/game/putt-day
+https://www.crazygames.com/br/game/putt-day
+https://www.crazygames.com/cz/game/putt-day
+https://www.crazygames.com/de/game/putt-day
+https://www.crazygames.com/dk/game/putt-day
+https://www.crazygames.com/es/game/putt-day
+https://www.crazygames.com/fi/game/putt-day
+https://www.crazygames.com/fr/game/putt-day
+https://www.crazygames.com/game/putt-day
+https://www.crazygames.com/gr/game/putt-day
+https://www.crazygames.com/hu/game/putt-day
+https://www.crazygames.com/id/game/putt-day
+https://www.crazygames.com/it/game/putt-day
+https://www.crazygames.com/jp/game/putt-day
+https://www.crazygames.com/kr/game/putt-day
+https://www.crazygames.com/nl/game/putt-day
+https://www.crazygames.com/no/game/putt-day
+https://www.crazygames.com/pl/game/putt-day
+https://www.crazygames.com/ro/game/putt-day
+https://www.crazygames.com/ru/game/putt-day
+https://www.crazygames.com/se/game/putt-day
+https://www.crazygames.com/th/game/putt-day
+https://www.crazygames.com/tr/game/putt-day
+https://www.crazygames.com/ua/game/putt-day
+https://www.crazygames.com/vn/game/putt-day</t>
         </is>
       </c>
       <c r="C11" s="3" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="D11" s="4" t="n">
+        <v>6830</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="7" t="n"/>
       <c r="I11" s="7" t="n"/>
       <c r="J11" s="8" t="n">
-        <v>29.2</v>
+        <v>16.1</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>app builder breakdown</t>
+          <t>putt day</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>sem_only（仅 SEM）</t>
+          <t>both（SIM+SEM）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>brainrotkit</t>
+          <t>codeproxy</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>https://huntifyai.com/tools/brainrotkit
-https://huntifyai.com/zh-CN/tools/brainrotkit</t>
+          <t>https://huntifyai.com/tools/codeproxy
+https://huntifyai.com/zh-CN/tools/codeproxy</t>
         </is>
       </c>
       <c r="C12" s="3" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="D12" s="4" t="n">
+        <v>380</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="7" t="n"/>
-      <c r="I12" s="7" t="n"/>
+      <c r="I12" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="J12" s="8" t="n">
-        <v>38.4</v>
+        <v>39.2</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>brainrotkit</t>
+          <t>codeproxy</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>sem_only（仅 SEM）</t>
+          <t>both（SIM+SEM）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>business keywords list for seo marketing and lead generation</t>
+          <t>escape from vlogger runaway</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>https://dragganaitool.com/business-keywords-list-for-seo-marketing-and-lead-generation</t>
+          <t>https://www.crazygames.com/br/game/escape-from-vlogger-runaway
+https://www.crazygames.com/fr/game/escape-from-vlogger-runaway
+https://www.crazygames.com/game/escape-from-vlogger-runaway
+https://www.crazygames.com/kr/game/escape-from-vlogger-runaway
+https://www.crazygames.com/nl/game/escape-from-vlogger-runaway
+https://www.crazygames.com/ru/game/escape-from-vlogger-runaway
+https://www.crazygames.com/se/game/escape-from-vlogger-runaway</t>
         </is>
       </c>
       <c r="C13" s="3" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="D13" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="7" t="n"/>
       <c r="I13" s="7" t="n"/>
       <c r="J13" s="8" t="n">
-        <v>17.4</v>
+        <v>57.2</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>business keywords list for seo marketing and lead generation</t>
+          <t>escape from vlogger runaway</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>sem_only（仅 SEM）</t>
+          <t>both（SIM+SEM）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>case4k</t>
+          <t>ai previsualization tools</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>https://higgsfield.ai/blog/case4k</t>
+          <t>https://higgsfield.ai/blog/ai-previsualization-tools</t>
         </is>
       </c>
       <c r="C14" s="3" t="n"/>
@@ -1113,11 +1164,11 @@
       <c r="H14" s="7" t="n"/>
       <c r="I14" s="7" t="n"/>
       <c r="J14" s="8" t="n">
-        <v>10.7</v>
+        <v>19.8</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>case4k</t>
+          <t>ai previsualization tools</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1129,12 +1180,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ecommerce job title taxonomy how to classify ecommerce roles</t>
+          <t>app builder breakdown</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>https://dragganaitool.com/ecommerce-job-title-taxonomy-how-to-classify-ecommerce-roles</t>
+          <t>https://higgsfield.ai/blog/app-builder-breakdown</t>
         </is>
       </c>
       <c r="C15" s="3" t="n"/>
@@ -1147,11 +1198,11 @@
       <c r="H15" s="7" t="n"/>
       <c r="I15" s="7" t="n"/>
       <c r="J15" s="8" t="n">
-        <v>29.6</v>
+        <v>29.2</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>ecommerce job title taxonomy how to classify ecommerce roles</t>
+          <t>app builder breakdown</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1163,12 +1214,13 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>gzyi top</t>
+          <t>brainrotkit</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>https://huntifyai.com/zh-CN/tools/gzyi-top</t>
+          <t>https://huntifyai.com/tools/brainrotkit
+https://huntifyai.com/zh-CN/tools/brainrotkit</t>
         </is>
       </c>
       <c r="C16" s="3" t="n"/>
@@ -1181,11 +1233,11 @@
       <c r="H16" s="7" t="n"/>
       <c r="I16" s="7" t="n"/>
       <c r="J16" s="8" t="n">
-        <v>0</v>
+        <v>38.4</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>gzyi top</t>
+          <t>brainrotkit</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1197,12 +1249,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>how to avoid distortions ai videos</t>
+          <t>business keywords list for seo marketing and lead generation</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>https://higgsfield.ai/blog/how-to-avoid-distortions-ai-videos</t>
+          <t>https://dragganaitool.com/business-keywords-list-for-seo-marketing-and-lead-generation</t>
         </is>
       </c>
       <c r="C17" s="3" t="n"/>
@@ -1215,11 +1267,11 @@
       <c r="H17" s="7" t="n"/>
       <c r="I17" s="7" t="n"/>
       <c r="J17" s="8" t="n">
-        <v>45.2</v>
+        <v>17.4</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>how to avoid distortions ai videos</t>
+          <t>business keywords list for seo marketing and lead generation</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1231,12 +1283,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>key features every user friendly online shopping website should include</t>
+          <t>case4k</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>https://dragganaitool.com/key-features-every-user-friendly-online-shopping-website-should-include</t>
+          <t>https://higgsfield.ai/blog/case4k</t>
         </is>
       </c>
       <c r="C18" s="3" t="n"/>
@@ -1249,11 +1301,11 @@
       <c r="H18" s="7" t="n"/>
       <c r="I18" s="7" t="n"/>
       <c r="J18" s="8" t="n">
-        <v>25.3</v>
+        <v>10.7</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>key features every user friendly online shopping website should include</t>
+          <t>case4k</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1265,12 +1317,16 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>make creative ads</t>
+          <t>dig drop merge</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>https://higgsfield.ai/blog/make-100-creative-ads</t>
+          <t>https://www.crazygames.com/ar/game/dig-drop-merge
+https://www.crazygames.com/br/game/dig-drop-merge
+https://www.crazygames.com/fr/game/dig-drop-merge
+https://www.crazygames.com/pl/game/dig-drop-merge
+https://www.crazygames.com/se/game/dig-drop-merge</t>
         </is>
       </c>
       <c r="C19" s="3" t="n"/>
@@ -1283,11 +1339,11 @@
       <c r="H19" s="7" t="n"/>
       <c r="I19" s="7" t="n"/>
       <c r="J19" s="8" t="n">
-        <v>45</v>
+        <v>42.2</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>make creative ads</t>
+          <t>dig drop merge</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1299,12 +1355,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>planograms explained retail shelf planning best practices</t>
+          <t>ecommerce job title taxonomy how to classify ecommerce roles</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>https://dragganaitool.com/planograms-explained-retail-shelf-planning-best-practices</t>
+          <t>https://dragganaitool.com/ecommerce-job-title-taxonomy-how-to-classify-ecommerce-roles</t>
         </is>
       </c>
       <c r="C20" s="3" t="n"/>
@@ -1317,11 +1373,11 @@
       <c r="H20" s="7" t="n"/>
       <c r="I20" s="7" t="n"/>
       <c r="J20" s="8" t="n">
-        <v>8.9</v>
+        <v>29.6</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>planograms explained retail shelf planning best practices</t>
+          <t>ecommerce job title taxonomy how to classify ecommerce roles</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -1333,12 +1389,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ragdoll chaos</t>
+          <t>gzyi top</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>https://poki.com/en/g/ragdoll-chaos</t>
+          <t>https://huntifyai.com/zh-CN/tools/gzyi-top</t>
         </is>
       </c>
       <c r="C21" s="3" t="n"/>
@@ -1351,11 +1407,11 @@
       <c r="H21" s="7" t="n"/>
       <c r="I21" s="7" t="n"/>
       <c r="J21" s="8" t="n">
-        <v>69.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>ragdoll chaos</t>
+          <t>gzyi top</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -1367,12 +1423,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>remittance processing how payment processing systems work</t>
+          <t>how to avoid distortions ai videos</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>https://dragganaitool.com/remittance-processing-how-payment-processing-systems-work</t>
+          <t>https://higgsfield.ai/blog/how-to-avoid-distortions-ai-videos</t>
         </is>
       </c>
       <c r="C22" s="3" t="n"/>
@@ -1385,11 +1441,11 @@
       <c r="H22" s="7" t="n"/>
       <c r="I22" s="7" t="n"/>
       <c r="J22" s="8" t="n">
-        <v>20.3</v>
+        <v>45.2</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>remittance processing how payment processing systems work</t>
+          <t>how to avoid distortions ai videos</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -1401,12 +1457,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>scratch card kingdom ufr</t>
+          <t>how to play lows adventures</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/cz/game/scratch-card-kingdom-ufr</t>
+          <t>https://www.coolmathgames.com/blog/how-to-play-lows-adventures</t>
         </is>
       </c>
       <c r="C23" s="3" t="n"/>
@@ -1419,11 +1475,11 @@
       <c r="H23" s="7" t="n"/>
       <c r="I23" s="7" t="n"/>
       <c r="J23" s="8" t="n">
-        <v>44.6</v>
+        <v>16.6</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>scratch card kingdom ufr</t>
+          <t>how to play lows adventures</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -1435,12 +1491,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>sge snippets explained ai search seo impact</t>
+          <t>key features every user friendly online shopping website should include</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>https://dragganaitool.com/sge-snippets-explained-ai-search-seo-impact</t>
+          <t>https://dragganaitool.com/key-features-every-user-friendly-online-shopping-website-should-include</t>
         </is>
       </c>
       <c r="C24" s="3" t="n"/>
@@ -1453,11 +1509,11 @@
       <c r="H24" s="7" t="n"/>
       <c r="I24" s="7" t="n"/>
       <c r="J24" s="8" t="n">
-        <v>14.5</v>
+        <v>25.3</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>sge snippets explained ai search seo impact</t>
+          <t>key features every user friendly online shopping website should include</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -1469,12 +1525,34 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>sole proprietorship advantages and disadvantages explained</t>
+          <t>magnetarrow</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>https://dragganaitool.com/sole-proprietorship-advantages-and-disadvantages-explained</t>
+          <t>https://www.crazygames.com/br/game/magnetarrow
+https://www.crazygames.com/cz/game/magnetarrow
+https://www.crazygames.com/de/game/magnetarrow
+https://www.crazygames.com/dk/game/magnetarrow
+https://www.crazygames.com/es/game/magnetarrow
+https://www.crazygames.com/fi/game/magnetarrow
+https://www.crazygames.com/fr/game/magnetarrow
+https://www.crazygames.com/game/magnetarrow
+https://www.crazygames.com/gr/game/magnetarrow
+https://www.crazygames.com/id/game/magnetarrow
+https://www.crazygames.com/it/game/magnetarrow
+https://www.crazygames.com/jp/game/magnetarrow
+https://www.crazygames.com/kr/game/magnetarrow
+https://www.crazygames.com/nl/game/magnetarrow
+https://www.crazygames.com/no/game/magnetarrow
+https://www.crazygames.com/pl/game/magnetarrow
+https://www.crazygames.com/ro/game/magnetarrow
+https://www.crazygames.com/ru/game/magnetarrow
+https://www.crazygames.com/se/game/magnetarrow
+https://www.crazygames.com/th/game/magnetarrow
+https://www.crazygames.com/tr/game/magnetarrow
+https://www.crazygames.com/ua/game/magnetarrow
+https://www.crazygames.com/vn/game/magnetarrow</t>
         </is>
       </c>
       <c r="C25" s="3" t="n"/>
@@ -1487,11 +1565,11 @@
       <c r="H25" s="7" t="n"/>
       <c r="I25" s="7" t="n"/>
       <c r="J25" s="8" t="n">
-        <v>10.6</v>
+        <v>25.2</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>sole proprietorship advantages and disadvantages explained</t>
+          <t>magnetarrow</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -1503,12 +1581,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>task priority levels explained high medium low urgent and popular prioritization frameworks</t>
+          <t>make creative ads</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>https://dragganaitool.com/task-priority-levels-explained-high-medium-low-urgent-and-popular-prioritization-frameworks</t>
+          <t>https://higgsfield.ai/blog/make-100-creative-ads</t>
         </is>
       </c>
       <c r="C26" s="3" t="n"/>
@@ -1521,11 +1599,11 @@
       <c r="H26" s="7" t="n"/>
       <c r="I26" s="7" t="n"/>
       <c r="J26" s="8" t="n">
-        <v>27.9</v>
+        <v>45</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>task priority levels explained high medium low urgent and popular prioritization frameworks</t>
+          <t>make creative ads</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -1537,12 +1615,36 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>tax filing tools that help you save time and maximize deductions</t>
+          <t>obby supercar race on keyboard</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>https://dragganaitool.com/tax-filing-tools-that-help-you-save-time-and-maximize-deductions</t>
+          <t>https://www.crazygames.com/ar/game/obby-supercar-race-on-keyboard
+https://www.crazygames.com/br/game/obby-supercar-race-on-keyboard
+https://www.crazygames.com/cz/game/obby-supercar-race-on-keyboard
+https://www.crazygames.com/de/game/obby-supercar-race-on-keyboard
+https://www.crazygames.com/dk/game/obby-supercar-race-on-keyboard
+https://www.crazygames.com/es/game/obby-supercar-race-on-keyboard
+https://www.crazygames.com/fi/game/obby-supercar-race-on-keyboard
+https://www.crazygames.com/fr/game/obby-supercar-race-on-keyboard
+https://www.crazygames.com/game/obby-supercar-race-on-keyboard
+https://www.crazygames.com/gr/game/obby-supercar-race-on-keyboard
+https://www.crazygames.com/hu/game/obby-supercar-race-on-keyboard
+https://www.crazygames.com/id/game/obby-supercar-race-on-keyboard
+https://www.crazygames.com/it/game/obby-supercar-race-on-keyboard
+https://www.crazygames.com/jp/game/obby-supercar-race-on-keyboard
+https://www.crazygames.com/kr/game/obby-supercar-race-on-keyboard
+https://www.crazygames.com/nl/game/obby-supercar-race-on-keyboard
+https://www.crazygames.com/no/game/obby-supercar-race-on-keyboard
+https://www.crazygames.com/pl/game/obby-supercar-race-on-keyboard
+https://www.crazygames.com/ro/game/obby-supercar-race-on-keyboard
+https://www.crazygames.com/ru/game/obby-supercar-race-on-keyboard
+https://www.crazygames.com/se/game/obby-supercar-race-on-keyboard
+https://www.crazygames.com/th/game/obby-supercar-race-on-keyboard
+https://www.crazygames.com/tr/game/obby-supercar-race-on-keyboard
+https://www.crazygames.com/ua/game/obby-supercar-race-on-keyboard
+https://www.crazygames.com/vn/game/obby-supercar-race-on-keyboard</t>
         </is>
       </c>
       <c r="C27" s="3" t="n"/>
@@ -1555,11 +1657,11 @@
       <c r="H27" s="7" t="n"/>
       <c r="I27" s="7" t="n"/>
       <c r="J27" s="8" t="n">
-        <v>28.2</v>
+        <v>33.7</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>tax filing tools that help you save time and maximize deductions</t>
+          <t>obby supercar race on keyboard</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -1571,12 +1673,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>top ecommerce podcasts every online seller should listen to</t>
+          <t>planograms explained retail shelf planning best practices</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>https://dragganaitool.com/top-6-ecommerce-podcasts-every-online-seller-should-listen-to-2026</t>
+          <t>https://dragganaitool.com/planograms-explained-retail-shelf-planning-best-practices</t>
         </is>
       </c>
       <c r="C28" s="3" t="n"/>
@@ -1589,11 +1691,11 @@
       <c r="H28" s="7" t="n"/>
       <c r="I28" s="7" t="n"/>
       <c r="J28" s="8" t="n">
-        <v>34.8</v>
+        <v>8.9</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>top ecommerce podcasts every online seller should listen to</t>
+          <t>planograms explained retail shelf planning best practices</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -1605,12 +1707,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>top retail competitor pricing data tools</t>
+          <t>ragdoll chaos</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>https://dragganaitool.com/top-7-retail-competitor-pricing-data-tools-2026</t>
+          <t>https://poki.com/en/g/ragdoll-chaos</t>
         </is>
       </c>
       <c r="C29" s="3" t="n"/>
@@ -1623,11 +1725,11 @@
       <c r="H29" s="7" t="n"/>
       <c r="I29" s="7" t="n"/>
       <c r="J29" s="8" t="n">
-        <v>18.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>top retail competitor pricing data tools</t>
+          <t>ragdoll chaos</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -1639,12 +1741,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>top wcag testing tools for website owners</t>
+          <t>remittance processing how payment processing systems work</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>https://dragganaitool.com/top-5-wcag-testing-tools-for-website-owners</t>
+          <t>https://dragganaitool.com/remittance-processing-how-payment-processing-systems-work</t>
         </is>
       </c>
       <c r="C30" s="3" t="n"/>
@@ -1657,11 +1759,11 @@
       <c r="H30" s="7" t="n"/>
       <c r="I30" s="7" t="n"/>
       <c r="J30" s="8" t="n">
-        <v>32.2</v>
+        <v>20.3</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>top wcag testing tools for website owners</t>
+          <t>remittance processing how payment processing systems work</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -1673,12 +1775,18 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>what is category name definition examples</t>
+          <t>scratch card kingdom ufr</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>https://dragganaitool.com/what-is-a-category-name-definition-examples</t>
+          <t>https://www.crazygames.com/ar/game/scratch-card-kingdom-ufr
+https://www.crazygames.com/br/game/scratch-card-kingdom-ufr
+https://www.crazygames.com/fr/game/scratch-card-kingdom-ufr
+https://www.crazygames.com/pl/game/scratch-card-kingdom-ufr
+https://www.crazygames.com/ro/game/scratch-card-kingdom-ufr
+https://www.crazygames.com/se/game/scratch-card-kingdom-ufr
+https://www.crazygames.com/th/game/scratch-card-kingdom-ufr</t>
         </is>
       </c>
       <c r="C31" s="3" t="n"/>
@@ -1691,21 +1799,351 @@
       <c r="H31" s="7" t="n"/>
       <c r="I31" s="7" t="n"/>
       <c r="J31" s="8" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>scratch card kingdom ufr</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>sge snippets explained ai search seo impact</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>https://dragganaitool.com/sge-snippets-explained-ai-search-seo-impact</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="7" t="n"/>
+      <c r="I32" s="7" t="n"/>
+      <c r="J32" s="8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>sge snippets explained ai search seo impact</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>sole proprietorship advantages and disadvantages explained</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>https://dragganaitool.com/sole-proprietorship-advantages-and-disadvantages-explained</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="7" t="n"/>
+      <c r="I33" s="7" t="n"/>
+      <c r="J33" s="8" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>sole proprietorship advantages and disadvantages explained</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>sweetjong</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crazygames.com/ar/game/sweetjong
+https://www.crazygames.com/br/game/sweetjong
+https://www.crazygames.com/cz/game/sweetjong
+https://www.crazygames.com/de/game/sweetjong
+https://www.crazygames.com/dk/game/sweetjong
+https://www.crazygames.com/es/game/sweetjong
+https://www.crazygames.com/fi/game/sweetjong
+https://www.crazygames.com/fr/game/sweetjong
+https://www.crazygames.com/game/sweetjong
+https://www.crazygames.com/gr/game/sweetjong
+https://www.crazygames.com/hu/game/sweetjong
+https://www.crazygames.com/id/game/sweetjong
+https://www.crazygames.com/it/game/sweetjong
+https://www.crazygames.com/jp/game/sweetjong
+https://www.crazygames.com/kr/game/sweetjong
+https://www.crazygames.com/nl/game/sweetjong
+https://www.crazygames.com/no/game/sweetjong
+https://www.crazygames.com/pl/game/sweetjong
+https://www.crazygames.com/ro/game/sweetjong
+https://www.crazygames.com/ru/game/sweetjong
+https://www.crazygames.com/se/game/sweetjong
+https://www.crazygames.com/th/game/sweetjong
+https://www.crazygames.com/tr/game/sweetjong
+https://www.crazygames.com/ua/game/sweetjong
+https://www.crazygames.com/vn/game/sweetjong</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="7" t="n"/>
+      <c r="I34" s="7" t="n"/>
+      <c r="J34" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>sweetjong</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>task priority levels explained high medium low urgent and popular prioritization frameworks</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>https://dragganaitool.com/task-priority-levels-explained-high-medium-low-urgent-and-popular-prioritization-frameworks</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="7" t="n"/>
+      <c r="I35" s="7" t="n"/>
+      <c r="J35" s="8" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>task priority levels explained high medium low urgent and popular prioritization frameworks</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>tax filing tools that help you save time and maximize deductions</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>https://dragganaitool.com/tax-filing-tools-that-help-you-save-time-and-maximize-deductions</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="7" t="n"/>
+      <c r="I36" s="7" t="n"/>
+      <c r="J36" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>tax filing tools that help you save time and maximize deductions</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>top ecommerce podcasts every online seller should listen to</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>https://dragganaitool.com/top-6-ecommerce-podcasts-every-online-seller-should-listen-to-2026</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="7" t="n"/>
+      <c r="I37" s="7" t="n"/>
+      <c r="J37" s="8" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>top ecommerce podcasts every online seller should listen to</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>top retail competitor pricing data tools</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>https://dragganaitool.com/top-7-retail-competitor-pricing-data-tools-2026</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="7" t="n"/>
+      <c r="I38" s="7" t="n"/>
+      <c r="J38" s="8" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>top retail competitor pricing data tools</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>top wcag testing tools for website owners</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>https://dragganaitool.com/top-5-wcag-testing-tools-for-website-owners</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="7" t="n"/>
+      <c r="I39" s="7" t="n"/>
+      <c r="J39" s="8" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>top wcag testing tools for website owners</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>what is category name definition examples</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>https://dragganaitool.com/what-is-a-category-name-definition-examples</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="7" t="n"/>
+      <c r="I40" s="7" t="n"/>
+      <c r="J40" s="8" t="n">
         <v>43</v>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>what is category name definition examples</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>sem_only（仅 SEM）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L31"/>
+  <autoFilter ref="A1:L40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/word-monitor-sitemap/report/latest.xlsx
+++ b/word-monitor-sitemap/report/latest.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="keywords" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -470,7 +470,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-07-30T14:11:24</t>
+          <t>2026-08-01T15:51:09</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -540,7 +540,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"inputCount": 20, "requestCount": 20, "successCount": 20, "successWithScoreCount": 20, "missingScoreCount": 0, "failedCount": 0}</t>
+          <t>{"inputCount": 13, "requestCount": 13, "successCount": 13, "successWithScoreCount": 13, "missingScoreCount": 0, "failedCount": 0}</t>
         </is>
       </c>
     </row>
@@ -555,10 +555,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
+    <col width="67" customWidth="1" min="1" max="1"/>
     <col width="64" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -568,7 +568,7 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="92" customWidth="1" min="11" max="11"/>
+    <col width="67" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -637,42 +637,41 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>dogs out</t>
+          <t>seedance</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/fi/game/dogs-out
-https://www.crazygames.com/no/game/dogs-out</t>
+          <t>https://higgsfield.ai/blog/seedance-2-5</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2.610526</v>
+        <v>17532.546875</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>40</v>
+        <v>1181140</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>1.24</v>
+        <v>0.95</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>6900</v>
+        <v>106180</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>0.73</v>
+        <v>1.48</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>65.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>dogs out</t>
+          <t>seedance</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -684,54 +683,51 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>railway bridge</t>
+          <t>swat cats</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/br/game/railway-bridge
-https://www.crazygames.com/cz/game/railway-bridge
-https://www.crazygames.com/de/game/railway-bridge
-https://www.crazygames.com/dk/game/railway-bridge
-https://www.crazygames.com/fi/game/railway-bridge
-https://www.crazygames.com/game/railway-bridge
-https://www.crazygames.com/gr/game/railway-bridge
-https://www.crazygames.com/id/game/railway-bridge
-https://www.crazygames.com/it/game/railway-bridge
-https://www.crazygames.com/jp/game/railway-bridge
-https://www.crazygames.com/pl/game/railway-bridge
-https://www.crazygames.com/ru/game/railway-bridge
-https://www.crazygames.com/se/game/railway-bridge
-https://www.crazygames.com/tr/game/railway-bridge
-https://www.crazygames.com/ua/game/railway-bridge
-https://www.crazygames.com/vn/game/railway-bridge</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n"/>
+          <t>https://www.crazygames.com/br/game/swat-cats
+https://www.crazygames.com/cz/game/swat-cats
+https://www.crazygames.com/fi/game/swat-cats
+https://www.crazygames.com/gr/game/swat-cats
+https://www.crazygames.com/id/game/swat-cats
+https://www.crazygames.com/it/game/swat-cats
+https://www.crazygames.com/jp/game/swat-cats
+https://www.crazygames.com/pl/game/swat-cats
+https://www.crazygames.com/ru/game/swat-cats
+https://www.crazygames.com/se/game/swat-cats
+https://www.crazygames.com/tr/game/swat-cats</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>509.04</v>
+      </c>
       <c r="D3" s="4" t="n">
-        <v>3610</v>
+        <v>2520</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>26650</v>
+        <v>16940</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I3" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>59.5</v>
+        <v>23.9</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>railway bridge</t>
+          <t>swat cats</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -743,92 +739,104 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>demolition inc</t>
+          <t>videotto</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/br/game/demolition-inc
-https://www.crazygames.com/cz/game/demolition-inc
-https://www.crazygames.com/de/game/demolition-inc
-https://www.crazygames.com/dk/game/demolition-inc
-https://www.crazygames.com/fi/game/demolition-inc
-https://www.crazygames.com/game/demolition-inc
-https://www.crazygames.com/gr/game/demolition-inc
-https://www.crazygames.com/id/game/demolition-inc
-https://www.crazygames.com/it/game/demolition-inc
-https://www.crazygames.com/jp/game/demolition-inc
-https://www.crazygames.com/pl/game/demolition-inc
-https://www.crazygames.com/ru/game/demolition-inc
-https://www.crazygames.com/se/game/demolition-inc
-https://www.crazygames.com/tr/game/demolition-inc
-https://www.crazygames.com/ua/game/demolition-inc
-https://www.crazygames.com/vn/game/demolition-inc</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
+          <t>https://huntifyai.com/tools/videotto
+https://huntifyai.com/zh-CN/tools/videotto</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>128.252542</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>22930</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.33</v>
+      </c>
       <c r="G4" s="6" t="n">
-        <v>750</v>
-      </c>
-      <c r="H4" s="7" t="n">
-        <v>32</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>52.5</v>
+        <v>48.4</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>demolition inc</t>
+          <t>videotto</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>sem_only（仅 SEM）</t>
+          <t>both（SIM+SEM）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ai ad agency</t>
+          <t>hexa stack</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>https://higgsfield.ai/blog/ai-ad-agency</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n"/>
+          <t>https://www.crazygames.com/ar/game/hexa-stack
+https://www.crazygames.com/br/game/hexa-stack
+https://www.crazygames.com/cz/game/hexa-stack
+https://www.crazygames.com/es/game/hexa-stack
+https://www.crazygames.com/fi/game/hexa-stack
+https://www.crazygames.com/fr/game/hexa-stack
+https://www.crazygames.com/gr/game/hexa-stack
+https://www.crazygames.com/hu/game/hexa-stack
+https://www.crazygames.com/id/game/hexa-stack
+https://www.crazygames.com/it/game/hexa-stack
+https://www.crazygames.com/jp/game/hexa-stack
+https://www.crazygames.com/kr/game/hexa-stack
+https://www.crazygames.com/no/game/hexa-stack
+https://www.crazygames.com/pl/game/hexa-stack
+https://www.crazygames.com/ro/game/hexa-stack
+https://www.crazygames.com/ru/game/hexa-stack
+https://www.crazygames.com/se/game/hexa-stack
+https://www.crazygames.com/th/game/hexa-stack
+https://www.crazygames.com/tr/game/hexa-stack</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>69.57541000000001</v>
+      </c>
       <c r="D5" s="4" t="n">
-        <v>70</v>
+        <v>3010</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>540</v>
+        <v>4360</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>11.1</v>
+        <v>0.63</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>18.6</v>
+        <v>57.2</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>ai ad agency</t>
+          <t>hexa stack</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -840,84 +848,101 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>20f8</t>
+          <t>perfect shape</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://poki.com/en/g/20f8</t>
+          <t>https://poki.com/en/g/perfect-shape</t>
         </is>
       </c>
       <c r="C6" s="3" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
+      <c r="D6" s="4" t="n">
+        <v>1520</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G6" s="6" t="n">
-        <v>110</v>
-      </c>
-      <c r="H6" s="7" t="n"/>
+        <v>2260</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>34</v>
+      </c>
       <c r="I6" s="7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>4.3</v>
+        <v>41.6</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20f8</t>
+          <t>perfect shape</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>sem_only（仅 SEM）</t>
+          <t>both（SIM+SEM）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>best ai ad generators</t>
+          <t>robynn</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://higgsfield.ai/blog/best-ai-ad-generators</t>
+          <t>https://huntifyai.com/tools/robynn
+https://huntifyai.com/zh-CN/tools/robynn</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="D7" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G7" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H7" s="7" t="n"/>
+        <v>590</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>39</v>
+      </c>
       <c r="I7" s="7" t="n">
-        <v>11.94</v>
+        <v>0</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>51.4</v>
+        <v>59.8</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>best ai ad generators</t>
+          <t>robynn</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>sem_only（仅 SEM）</t>
+          <t>both（SIM+SEM）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>count and bounce bls</t>
+          <t>ai presentation makers compared which one fits your workflow best</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/fi/game/count-and-bounce-bls</t>
+          <t>https://dragganaitool.com/ai-presentation-makers-compared-which-one-fits-your-workflow-best</t>
         </is>
       </c>
       <c r="C8" s="3" t="n"/>
@@ -934,7 +959,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>count and bounce bls</t>
+          <t>ai presentation makers compared which one fits your workflow best</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -946,12 +971,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>draw one line drawing puzzle</t>
+          <t>ai short film pipeline</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/fi/game/draw-one-line-drawing-puzzle</t>
+          <t>https://higgsfield.ai/blog/ai-short-film-pipeline</t>
         </is>
       </c>
       <c r="C9" s="3" t="n"/>
@@ -964,11 +989,11 @@
       <c r="H9" s="7" t="n"/>
       <c r="I9" s="7" t="n"/>
       <c r="J9" s="8" t="n">
-        <v>36.3</v>
+        <v>30.3</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>draw one line drawing puzzle</t>
+          <t>ai short film pipeline</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -980,13 +1005,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>furriq</t>
+          <t>flip pounce</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>https://huntifyai.com/tools/furriq
-https://huntifyai.com/zh-CN/tools/furriq</t>
+          <t>https://poki.com/en/g/flip-pounce</t>
         </is>
       </c>
       <c r="C10" s="3" t="n"/>
@@ -999,11 +1023,11 @@
       <c r="H10" s="7" t="n"/>
       <c r="I10" s="7" t="n"/>
       <c r="J10" s="8" t="n">
-        <v>40.6</v>
+        <v>65.5</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>furriq</t>
+          <t>flip pounce</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1015,12 +1039,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>healthcare care management platforms for hospitals payers and community care organizations</t>
+          <t>how ai powered promotions help merchants increase sales</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>https://dragganaitool.com/7-healthcare-care-management-platforms-for-hospitals-payers-and-community-care-organizations</t>
+          <t>https://dragganaitool.com/how-ai-powered-promotions-help-merchants-increase-sales</t>
         </is>
       </c>
       <c r="C11" s="3" t="n"/>
@@ -1033,11 +1057,11 @@
       <c r="H11" s="7" t="n"/>
       <c r="I11" s="7" t="n"/>
       <c r="J11" s="8" t="n">
-        <v>11.1</v>
+        <v>24.5</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>healthcare care management platforms for hospitals payers and community care organizations</t>
+          <t>how ai powered promotions help merchants increase sales</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1049,12 +1073,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>how alltegrios voice ai agent streamlined insurance support</t>
+          <t>pananto platform review features benefits and alternatives</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>https://dragganaitool.com/how-alltegrios-voice-ai-agent-streamlined-insurance-support</t>
+          <t>https://dragganaitool.com/pananto-platform-review-features-benefits-and-alternatives</t>
         </is>
       </c>
       <c r="C12" s="3" t="n"/>
@@ -1067,11 +1091,11 @@
       <c r="H12" s="7" t="n"/>
       <c r="I12" s="7" t="n"/>
       <c r="J12" s="8" t="n">
-        <v>17.2</v>
+        <v>37.1</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>how alltegrios voice ai agent streamlined insurance support</t>
+          <t>pananto platform review features benefits and alternatives</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1083,12 +1107,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>how to offer payment flexibility without hurting your brand</t>
+          <t>seedance unlimited days</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>https://dragganaitool.com/how-to-offer-payment-flexibility-without-hurting-your-brand</t>
+          <t>https://higgsfield.ai/blog/seedance-unlimited-14-days</t>
         </is>
       </c>
       <c r="C13" s="3" t="n"/>
@@ -1101,11 +1125,11 @@
       <c r="H13" s="7" t="n"/>
       <c r="I13" s="7" t="n"/>
       <c r="J13" s="8" t="n">
-        <v>1.3</v>
+        <v>39.1</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>how to offer payment flexibility without hurting your brand</t>
+          <t>seedance unlimited days</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1117,12 +1141,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>idle dairy tycoon</t>
+          <t>top salesforce apps that improve sales and productivity</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>https://www.crazygames.com/fi/game/idle-dairy-tycoon</t>
+          <t>https://dragganaitool.com/top-salesforce-apps-that-improve-sales-and-productivity</t>
         </is>
       </c>
       <c r="C14" s="3" t="n"/>
@@ -1135,11 +1159,11 @@
       <c r="H14" s="7" t="n"/>
       <c r="I14" s="7" t="n"/>
       <c r="J14" s="8" t="n">
-        <v>44.7</v>
+        <v>26.4</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>idle dairy tycoon</t>
+          <t>top salesforce apps that improve sales and productivity</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1148,286 +1172,8 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>krea2turbo pro</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>https://huntifyai.com/tools/krea2turbo-pro
-https://huntifyai.com/zh-CN/tools/krea2turbo-pro</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="7" t="n"/>
-      <c r="J15" s="8" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>krea2turbo pro</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>sem_only（仅 SEM）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>merge haven fzh</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.crazygames.com/ar/game/merge-haven-fzh
-https://www.crazygames.com/br/game/merge-haven-fzh
-https://www.crazygames.com/cz/game/merge-haven-fzh
-https://www.crazygames.com/de/game/merge-haven-fzh
-https://www.crazygames.com/dk/game/merge-haven-fzh
-https://www.crazygames.com/es/game/merge-haven-fzh
-https://www.crazygames.com/fi/game/merge-haven-fzh
-https://www.crazygames.com/fr/game/merge-haven-fzh
-https://www.crazygames.com/game/merge-haven-fzh
-https://www.crazygames.com/gr/game/merge-haven-fzh
-https://www.crazygames.com/hu/game/merge-haven-fzh
-https://www.crazygames.com/id/game/merge-haven-fzh
-https://www.crazygames.com/it/game/merge-haven-fzh
-https://www.crazygames.com/jp/game/merge-haven-fzh
-https://www.crazygames.com/kr/game/merge-haven-fzh
-https://www.crazygames.com/nl/game/merge-haven-fzh
-https://www.crazygames.com/no/game/merge-haven-fzh
-https://www.crazygames.com/pl/game/merge-haven-fzh
-https://www.crazygames.com/ru/game/merge-haven-fzh
-https://www.crazygames.com/se/game/merge-haven-fzh
-https://www.crazygames.com/th/game/merge-haven-fzh
-https://www.crazygames.com/tr/game/merge-haven-fzh
-https://www.crazygames.com/ua/game/merge-haven-fzh
-https://www.crazygames.com/vn/game/merge-haven-fzh</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="7" t="n"/>
-      <c r="J16" s="8" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>merge haven fzh</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>sem_only（仅 SEM）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>road rage hva</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.crazygames.com/br/game/road-rage-hva
-https://www.crazygames.com/cz/game/road-rage-hva
-https://www.crazygames.com/de/game/road-rage-hva
-https://www.crazygames.com/dk/game/road-rage-hva
-https://www.crazygames.com/fi/game/road-rage-hva
-https://www.crazygames.com/game/road-rage-hva
-https://www.crazygames.com/gr/game/road-rage-hva
-https://www.crazygames.com/id/game/road-rage-hva
-https://www.crazygames.com/it/game/road-rage-hva
-https://www.crazygames.com/jp/game/road-rage-hva
-https://www.crazygames.com/pl/game/road-rage-hva
-https://www.crazygames.com/ru/game/road-rage-hva
-https://www.crazygames.com/se/game/road-rage-hva
-https://www.crazygames.com/tr/game/road-rage-hva
-https://www.crazygames.com/ua/game/road-rage-hva
-https://www.crazygames.com/vn/game/road-rage-hva</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="7" t="n"/>
-      <c r="J17" s="8" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>road rage hva</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>sem_only（仅 SEM）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>robshoot</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.crazygames.com/se/game/robshoot
-https://www.crazygames.com/tr/game/robshoot</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="7" t="n"/>
-      <c r="I18" s="7" t="n"/>
-      <c r="J18" s="8" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>robshoot</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>sem_only（仅 SEM）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>scale labs and paypal what the partnership means</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>https://dragganaitool.com/scale-labs-and-paypal-what-the-partnership-means</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="7" t="n"/>
-      <c r="J19" s="8" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>scale labs and paypal what the partnership means</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>sem_only（仅 SEM）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>squarespace vs shopify for paypal payments</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>https://dragganaitool.com/squarespace-vs-shopify-for-paypal-payments</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="7" t="n"/>
-      <c r="J20" s="8" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>squarespace vs shopify for paypal payments</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>sem_only（仅 SEM）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>unlimited mcp</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>https://higgsfield.ai/blog/unlimited-mcp</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="7" t="n"/>
-      <c r="J21" s="8" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>unlimited mcp</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>sem_only（仅 SEM）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L21"/>
+  <autoFilter ref="A1:L14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>